--- a/releases/final/artifacts/03_AI_Bracket_War_Room_2026_Spreadsheet_Engine.xlsx
+++ b/releases/final/artifacts/03_AI_Bracket_War_Room_2026_Spreadsheet_Engine.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START_HERE" sheetId="1" r:id="R1b35f6992ac44de5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRACKET_WAR_ROOM" sheetId="2" r:id="R0c6ff109fdae4b1f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATCH_PLANNER" sheetId="3" r:id="R3b4f4f9b6725424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRIENDS_LEAGUE" sheetId="4" r:id="R7764ebc0434c4775"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnnexC_495_STATIC" sheetId="5" r:id="R92221c0dd7ce4715"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_STATIC_CHECK" sheetId="6" r:id="R33f2f7a4e2794aca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="START_HERE" sheetId="1" r:id="Raebcaf57e7794861"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BRACKET_WAR_ROOM" sheetId="2" r:id="R92f4572ef99e4e52"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MATCH_PLANNER" sheetId="3" r:id="R57dc34df0c4d4adf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FRIENDS_LEAGUE" sheetId="4" r:id="R381cf3d2774e4f13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AnnexC_495_STATIC" sheetId="5" r:id="R2d83504e037a4373"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="QA_STATIC_CHECK" sheetId="6" r:id="R2c50eb964b094163"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,7 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="6">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="0"/>
+  </x:numFmts>
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -52,8 +55,48 @@
       <x:color rgb="FFFFFF"/>
       <x:name val="Aptos"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFF"/>
+      <x:name val="Aptos Display"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="16"/>
+      <x:color rgb="FFFFFF"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="0D1B2A"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="0D1B2A"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="0D1B2A"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:i/>
+      <x:sz val="10"/>
+      <x:color rgb="0D1B2A"/>
+      <x:name val="Aptos"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="0D1B2A"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="9">
+  <x:fills count="11">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -95,6 +138,16 @@
         <x:fgColor rgb="B8912E"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="0D1B2A"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="E2E8F0"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -103,7 +156,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="68">
+  <x:cellXfs count="106">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -244,10 +297,119 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
+  <x:dxfs count="1">
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="166534"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="DCFCE7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+  </x:dxfs>
 </x:styleSheet>
 </file>
 
@@ -383,44 +545,44 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Hackathon Sports-Tech">
   <a:themeElements>
-    <a:clrScheme name="ChatGPT">
+    <a:clrScheme name="Hackathon Sports-Tech">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="0D1B2A"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="F4F6F9"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="0D1B2A"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="10B981"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="F59E0B"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="EF4444"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="2563EB"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="64748B"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="2563EB"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="7C3AED"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
@@ -435,7 +597,7 @@
         <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="ChatGPT">
+    <a:fmtScheme name="Hackathon Sports-Tech">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -531,9 +693,9 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="72" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
@@ -544,24 +706,24 @@
     <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="9" t="str">
-        <x:v>AI BRACKET WAR ROOM 2026 — FIX6C STATIC ANNEXC</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="4"/>
-      <x:c r="K1" s="4"/>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="71" t="str">
+        <x:v>AI BRACKET WAR ROOM 2026 — HACKATHON DEMO SPREADSHEET ENGINE</x:v>
+      </x:c>
+      <x:c r="B1" s="74"/>
+      <x:c r="C1" s="74"/>
+      <x:c r="D1" s="74"/>
+      <x:c r="E1" s="74"/>
+      <x:c r="F1" s="74"/>
+      <x:c r="G1" s="74"/>
+      <x:c r="H1" s="74"/>
+      <x:c r="I1" s="74"/>
+      <x:c r="J1" s="74"/>
+      <x:c r="K1" s="74"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="17" t="str">
-        <x:v>Buyer-facing workbook with static embedded AnnexC_495. No IMPORTHTML, no web dependency, no array expansion layer.</x:v>
+        <x:v>Converted from the production XLSX engine into a hackathon-facing command center. Static, editable, no web imports, no official tournament data feed.</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -587,6 +749,1497 @@
       <x:c r="J3" s="4"/>
       <x:c r="K3" s="4"/>
     </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="79" t="str">
+        <x:v>DEMO NAVIGATION</x:v>
+      </x:c>
+      <x:c r="B4" s="79" t="str">
+        <x:v>Open Sheet</x:v>
+      </x:c>
+      <x:c r="C4" s="79" t="str">
+        <x:v>What judges should inspect</x:v>
+      </x:c>
+      <x:c r="D4" s="4"/>
+      <x:c r="E4" s="4"/>
+      <x:c r="F4" s="4"/>
+      <x:c r="G4" s="4"/>
+      <x:c r="H4" s="4"/>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
+      <x:c r="K4" s="4"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="89" t="str">
+        <x:v>Bracket War Room</x:v>
+      </x:c>
+      <x:c r="B5" s="89" t="e">
+        <x:f>HYPERLINK("#'BRACKET_WAR_ROOM'!A1","Open")</x:f>
+      </x:c>
+      <x:c r="C5" s="89" t="str">
+        <x:v>Command-center overview for prediction workflow and product story.</x:v>
+      </x:c>
+      <x:c r="D5" s="4"/>
+      <x:c r="E5" s="4"/>
+      <x:c r="F5" s="4"/>
+      <x:c r="G5" s="4"/>
+      <x:c r="H5" s="4"/>
+      <x:c r="I5" s="4"/>
+      <x:c r="J5" s="4"/>
+      <x:c r="K5" s="4"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="84" t="str">
+        <x:v>104-Match Planner</x:v>
+      </x:c>
+      <x:c r="B6" s="84" t="e">
+        <x:f>HYPERLINK("#'MATCH_PLANNER'!A1","Open")</x:f>
+      </x:c>
+      <x:c r="C6" s="84" t="str">
+        <x:v>M001–M104 editable match-planning grid with AI signal notes and points formula.</x:v>
+      </x:c>
+      <x:c r="D6" s="4"/>
+      <x:c r="E6" s="4"/>
+      <x:c r="F6" s="4"/>
+      <x:c r="G6" s="4"/>
+      <x:c r="H6" s="4"/>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="4"/>
+      <x:c r="K6" s="4"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="84" t="str">
+        <x:v>Friends League</x:v>
+      </x:c>
+      <x:c r="B7" s="84" t="e">
+        <x:f>HYPERLINK("#'FRIENDS_LEAGUE'!A1","Open")</x:f>
+      </x:c>
+      <x:c r="C7" s="84" t="str">
+        <x:v>Private group scoreboard with scoring formula: scores ×3, winners ×1, upsets ×2.</x:v>
+      </x:c>
+      <x:c r="D7" s="4"/>
+      <x:c r="E7" s="4"/>
+      <x:c r="F7" s="4"/>
+      <x:c r="G7" s="4"/>
+      <x:c r="H7" s="4"/>
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="4"/>
+      <x:c r="K7" s="4"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="84" t="str">
+        <x:v>Annex C Data Layer</x:v>
+      </x:c>
+      <x:c r="B8" s="84" t="e">
+        <x:f>HYPERLINK("#'AnnexC_495_STATIC'!A1","Open")</x:f>
+      </x:c>
+      <x:c r="C8" s="84" t="str">
+        <x:v>495 static embedded records proving offline data architecture; no IMPORTHTML/IMPORTRANGE.</x:v>
+      </x:c>
+      <x:c r="D8" s="4"/>
+      <x:c r="E8" s="4"/>
+      <x:c r="F8" s="4"/>
+      <x:c r="G8" s="4"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="84" t="str">
+        <x:v>QA Check</x:v>
+      </x:c>
+      <x:c r="B9" s="84" t="e">
+        <x:f>HYPERLINK("#'QA_STATIC_CHECK'!A1","Open")</x:f>
+      </x:c>
+      <x:c r="C9" s="84" t="str">
+        <x:v>Internal QA sheet. Keep hidden in polished cloud demo if desired.</x:v>
+      </x:c>
+      <x:c r="D9" s="4"/>
+      <x:c r="E9" s="4"/>
+      <x:c r="F9" s="4"/>
+      <x:c r="G9" s="4"/>
+      <x:c r="H9" s="4"/>
+      <x:c r="I9" s="4"/>
+      <x:c r="J9" s="4"/>
+      <x:c r="K9" s="4"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="84"/>
+      <x:c r="B10" s="84"/>
+      <x:c r="C10" s="84"/>
+      <x:c r="D10" s="4"/>
+      <x:c r="E10" s="4"/>
+      <x:c r="F10" s="4"/>
+      <x:c r="G10" s="4"/>
+      <x:c r="H10" s="4"/>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="4"/>
+      <x:c r="K10" s="4"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="82" t="str">
+        <x:v>HACKATHON DEMO STORY</x:v>
+      </x:c>
+      <x:c r="B11" s="82" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="C11" s="82" t="str">
+        <x:v>Implementation</x:v>
+      </x:c>
+      <x:c r="D11" s="4"/>
+      <x:c r="E11" s="4"/>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="90" t="str">
+        <x:v>Hyperlinked planner logic</x:v>
+      </x:c>
+      <x:c r="B12" s="90" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C12" s="90" t="str">
+        <x:v>GoodNotes PDF remains the visual command-center artifact; spreadsheet mirrors the operational data layer.</x:v>
+      </x:c>
+      <x:c r="D12" s="4"/>
+      <x:c r="E12" s="4"/>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="90" t="str">
+        <x:v>104-match spreadsheet engine</x:v>
+      </x:c>
+      <x:c r="B13" s="90" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C13" s="90" t="str">
+        <x:v>MATCH_PLANNER now exposes M001–M104 for end-to-end tournament workflow.</x:v>
+      </x:c>
+      <x:c r="D13" s="4"/>
+      <x:c r="E13" s="4"/>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="90" t="str">
+        <x:v>Private friends-league scoring</x:v>
+      </x:c>
+      <x:c r="B14" s="90" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C14" s="90" t="str">
+        <x:v>FRIENDS_LEAGUE includes editable player rows and formula-driven Total Points.</x:v>
+      </x:c>
+      <x:c r="D14" s="4"/>
+      <x:c r="E14" s="4"/>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="91" t="str">
+        <x:v>AI signal notes</x:v>
+      </x:c>
+      <x:c r="B15" s="91" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C15" s="91" t="str">
+        <x:v>AI Signal and Confidence fields are static buyer-editable planning inputs, not sportsbook odds.</x:v>
+      </x:c>
+      <x:c r="D15" s="4"/>
+      <x:c r="E15" s="4"/>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
+      <x:c r="H15" s="4"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="84" t="str">
+        <x:v>495-record static Annex C</x:v>
+      </x:c>
+      <x:c r="B16" s="84" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C16" s="84" t="str">
+        <x:v>Embedded ordinary cell values; no external data dependency.</x:v>
+      </x:c>
+      <x:c r="D16" s="4"/>
+      <x:c r="E16" s="4"/>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="84" t="str">
+        <x:v>306 transparent PNG stickers</x:v>
+      </x:c>
+      <x:c r="B17" s="84" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C17" s="84" t="str">
+        <x:v>Sticker pack is a separate buyer artifact; workbook references the product stack only.</x:v>
+      </x:c>
+      <x:c r="D17" s="4"/>
+      <x:c r="E17" s="4"/>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="84"/>
+      <x:c r="B18" s="84"/>
+      <x:c r="C18" s="84"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="82" t="str">
+        <x:v>BOUNDARY / CLAIM CONTROL</x:v>
+      </x:c>
+      <x:c r="B19" s="82" t="str">
+        <x:v>Allowed</x:v>
+      </x:c>
+      <x:c r="C19" s="82" t="str">
+        <x:v>Forbidden</x:v>
+      </x:c>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
+      <x:c r="H19" s="4"/>
+      <x:c r="I19" s="4"/>
+      <x:c r="J19" s="4"/>
+      <x:c r="K19" s="4"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="84" t="str">
+        <x:v>Spreadsheet claim</x:v>
+      </x:c>
+      <x:c r="B20" s="84" t="str">
+        <x:v>Static spreadsheet engine; Google Sheets demo version; Excel-compatible XLSX source.</x:v>
+      </x:c>
+      <x:c r="C20" s="84" t="str">
+        <x:v>Live Google Sheets automation; real-time import; official data feed.</x:v>
+      </x:c>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
+      <x:c r="H20" s="4"/>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="4"/>
+      <x:c r="K20" s="4"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="90" t="str">
+        <x:v>Football visual language</x:v>
+      </x:c>
+      <x:c r="B21" s="90" t="str">
+        <x:v>Generic football tournament planning, brackets, matchday workflow, champion/winner language.</x:v>
+      </x:c>
+      <x:c r="C21" s="90" t="str">
+        <x:v>FIFA marks, official World Cup emblem, exact official trophy replica, team crests, player likenesses.</x:v>
+      </x:c>
+      <x:c r="D21" s="4"/>
+      <x:c r="E21" s="4"/>
+      <x:c r="F21" s="4"/>
+      <x:c r="G21" s="4"/>
+      <x:c r="H21" s="4"/>
+      <x:c r="I21" s="4"/>
+      <x:c r="J21" s="4"/>
+      <x:c r="K21" s="4"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="90" t="str">
+        <x:v>Scoring language</x:v>
+      </x:c>
+      <x:c r="B22" s="90" t="str">
+        <x:v>Prediction workflow and private league points.</x:v>
+      </x:c>
+      <x:c r="C22" s="90" t="str">
+        <x:v>Betting, sportsbook, odds, wagering claims.</x:v>
+      </x:c>
+      <x:c r="D22" s="4"/>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="90"/>
+      <x:c r="B23" s="90"/>
+      <x:c r="C23" s="90"/>
+      <x:c r="D23" s="4"/>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="4"/>
+      <x:c r="G23" s="4"/>
+      <x:c r="H23" s="4"/>
+      <x:c r="I23" s="4"/>
+      <x:c r="J23" s="4"/>
+      <x:c r="K23" s="4"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="92" t="str">
+        <x:v>GOOGLE SHEETS DEMO LINK</x:v>
+      </x:c>
+      <x:c r="B24" s="92" t="str">
+        <x:v>https://docs.google.com/spreadsheets/d/1dptWAJhyu-ggGoIjOiKo7Fh4hQYs1l6oF7RYLAyFj_0/edit?usp=sharing</x:v>
+      </x:c>
+      <x:c r="C24" s="92" t="str">
+        <x:v>After upload/conversion, judges should use File → Make a copy before editing.</x:v>
+      </x:c>
+      <x:c r="D24" s="50"/>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="33"/>
+      <x:c r="B25" s="33"/>
+      <x:c r="C25" s="33"/>
+      <x:c r="D25" s="33"/>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="33"/>
+      <x:c r="B26" s="33"/>
+      <x:c r="C26" s="33"/>
+      <x:c r="D26" s="33"/>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="4"/>
+      <x:c r="J26" s="4"/>
+      <x:c r="K26" s="4"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="33"/>
+      <x:c r="B27" s="33"/>
+      <x:c r="C27" s="33"/>
+      <x:c r="D27" s="33"/>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="4"/>
+      <x:c r="J27" s="4"/>
+      <x:c r="K27" s="4"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="4"/>
+      <x:c r="B28" s="4"/>
+      <x:c r="C28" s="4"/>
+      <x:c r="D28" s="4"/>
+      <x:c r="E28" s="4"/>
+      <x:c r="F28" s="4"/>
+      <x:c r="G28" s="4"/>
+      <x:c r="H28" s="4"/>
+      <x:c r="I28" s="4"/>
+      <x:c r="J28" s="4"/>
+      <x:c r="K28" s="4"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="4"/>
+      <x:c r="G29" s="4"/>
+      <x:c r="H29" s="4"/>
+      <x:c r="I29" s="4"/>
+      <x:c r="J29" s="4"/>
+      <x:c r="K29" s="4"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="4"/>
+      <x:c r="B30" s="4"/>
+      <x:c r="C30" s="4"/>
+      <x:c r="D30" s="4"/>
+      <x:c r="E30" s="4"/>
+      <x:c r="F30" s="4"/>
+      <x:c r="G30" s="4"/>
+      <x:c r="H30" s="4"/>
+      <x:c r="I30" s="4"/>
+      <x:c r="J30" s="4"/>
+      <x:c r="K30" s="4"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="4"/>
+      <x:c r="B31" s="4"/>
+      <x:c r="C31" s="4"/>
+      <x:c r="D31" s="4"/>
+      <x:c r="E31" s="4"/>
+      <x:c r="F31" s="4"/>
+      <x:c r="G31" s="4"/>
+      <x:c r="H31" s="4"/>
+      <x:c r="I31" s="4"/>
+      <x:c r="J31" s="4"/>
+      <x:c r="K31" s="4"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="4"/>
+      <x:c r="B32" s="4"/>
+      <x:c r="C32" s="4"/>
+      <x:c r="D32" s="4"/>
+      <x:c r="E32" s="4"/>
+      <x:c r="F32" s="4"/>
+      <x:c r="G32" s="4"/>
+      <x:c r="H32" s="4"/>
+      <x:c r="I32" s="4"/>
+      <x:c r="J32" s="4"/>
+      <x:c r="K32" s="4"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="4"/>
+      <x:c r="B33" s="4"/>
+      <x:c r="C33" s="4"/>
+      <x:c r="D33" s="4"/>
+      <x:c r="E33" s="4"/>
+      <x:c r="F33" s="4"/>
+      <x:c r="G33" s="4"/>
+      <x:c r="H33" s="4"/>
+      <x:c r="I33" s="4"/>
+      <x:c r="J33" s="4"/>
+      <x:c r="K33" s="4"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="4"/>
+      <x:c r="B34" s="4"/>
+      <x:c r="C34" s="4"/>
+      <x:c r="D34" s="4"/>
+      <x:c r="E34" s="4"/>
+      <x:c r="F34" s="4"/>
+      <x:c r="G34" s="4"/>
+      <x:c r="H34" s="4"/>
+      <x:c r="I34" s="4"/>
+      <x:c r="J34" s="4"/>
+      <x:c r="K34" s="4"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="4"/>
+      <x:c r="B35" s="4"/>
+      <x:c r="C35" s="4"/>
+      <x:c r="D35" s="4"/>
+      <x:c r="E35" s="4"/>
+      <x:c r="F35" s="4"/>
+      <x:c r="G35" s="4"/>
+      <x:c r="H35" s="4"/>
+      <x:c r="I35" s="4"/>
+      <x:c r="J35" s="4"/>
+      <x:c r="K35" s="4"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="4"/>
+      <x:c r="B36" s="4"/>
+      <x:c r="C36" s="4"/>
+      <x:c r="D36" s="4"/>
+      <x:c r="E36" s="4"/>
+      <x:c r="F36" s="4"/>
+      <x:c r="G36" s="4"/>
+      <x:c r="H36" s="4"/>
+      <x:c r="I36" s="4"/>
+      <x:c r="J36" s="4"/>
+      <x:c r="K36" s="4"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A2:K2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="3">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R95b4afff99b842e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0448d52e7f184c2b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Red7813d2c3be4f84"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="50" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="71" t="str">
+        <x:v>BRACKET WAR ROOM — HACKATHON COMMAND CENTER</x:v>
+      </x:c>
+      <x:c r="B1" s="74"/>
+      <x:c r="C1" s="74"/>
+      <x:c r="D1" s="74"/>
+      <x:c r="E1" s="74"/>
+      <x:c r="F1" s="4"/>
+      <x:c r="G1" s="4"/>
+      <x:c r="H1" s="4"/>
+      <x:c r="I1" s="4"/>
+      <x:c r="J1" s="4"/>
+      <x:c r="K1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="103" t="str">
+        <x:v>Overview sheet for the prediction workflow. Use the navigation row to open the 104-match planner, friends league, and Annex C data layer.</x:v>
+      </x:c>
+      <x:c r="B2" s="90"/>
+      <x:c r="C2" s="90"/>
+      <x:c r="D2" s="90"/>
+      <x:c r="E2" s="90"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="90" t="str">
+        <x:v>Navigation</x:v>
+      </x:c>
+      <x:c r="B3" s="90" t="e">
+        <x:f>HYPERLINK("#'START_HERE'!A1","START")</x:f>
+      </x:c>
+      <x:c r="C3" s="90" t="e">
+        <x:f>HYPERLINK("#'MATCH_PLANNER'!A1","104 Matches")</x:f>
+      </x:c>
+      <x:c r="D3" s="90" t="e">
+        <x:f>HYPERLINK("#'FRIENDS_LEAGUE'!A1","Friends League")</x:f>
+      </x:c>
+      <x:c r="E3" s="90" t="e">
+        <x:f>HYPERLINK("#'AnnexC_495_STATIC'!A1","Annex C")</x:f>
+      </x:c>
+      <x:c r="F3" s="4"/>
+      <x:c r="G3" s="4"/>
+      <x:c r="H3" s="4"/>
+      <x:c r="I3" s="4"/>
+      <x:c r="J3" s="4"/>
+      <x:c r="K3" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="90"/>
+      <x:c r="B4" s="90"/>
+      <x:c r="C4" s="90"/>
+      <x:c r="D4" s="90"/>
+      <x:c r="E4" s="90"/>
+      <x:c r="F4" s="4"/>
+      <x:c r="G4" s="4"/>
+      <x:c r="H4" s="4"/>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
+      <x:c r="K4" s="4"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="82" t="str">
+        <x:v>Hackathon Proof</x:v>
+      </x:c>
+      <x:c r="B5" s="82" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="C5" s="82" t="str">
+        <x:v>Metric</x:v>
+      </x:c>
+      <x:c r="D5" s="82" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="E5" s="89"/>
+      <x:c r="F5" s="4"/>
+      <x:c r="G5" s="4"/>
+      <x:c r="H5" s="4"/>
+      <x:c r="I5" s="4"/>
+      <x:c r="J5" s="4"/>
+      <x:c r="K5" s="4"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="84" t="str">
+        <x:v>Planner coverage</x:v>
+      </x:c>
+      <x:c r="B6" s="84" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C6" s="84" t="str">
+        <x:v>104 matches</x:v>
+      </x:c>
+      <x:c r="D6" s="84" t="str">
+        <x:v>M001–M104 exposed in MATCH_PLANNER</x:v>
+      </x:c>
+      <x:c r="E6" s="84"/>
+      <x:c r="F6" s="4"/>
+      <x:c r="G6" s="4"/>
+      <x:c r="H6" s="4"/>
+      <x:c r="I6" s="4"/>
+      <x:c r="J6" s="4"/>
+      <x:c r="K6" s="4"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="84" t="str">
+        <x:v>Data layer</x:v>
+      </x:c>
+      <x:c r="B7" s="84" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C7" s="84" t="str">
+        <x:v>495 records</x:v>
+      </x:c>
+      <x:c r="D7" s="84" t="str">
+        <x:v>AnnexC_495_STATIC embedded values</x:v>
+      </x:c>
+      <x:c r="E7" s="84"/>
+      <x:c r="F7" s="4"/>
+      <x:c r="G7" s="4"/>
+      <x:c r="H7" s="4"/>
+      <x:c r="I7" s="4"/>
+      <x:c r="J7" s="4"/>
+      <x:c r="K7" s="4"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="84" t="str">
+        <x:v>Scoring</x:v>
+      </x:c>
+      <x:c r="B8" s="84" t="str">
+        <x:v>READY</x:v>
+      </x:c>
+      <x:c r="C8" s="84" t="str">
+        <x:v>Formula-driven</x:v>
+      </x:c>
+      <x:c r="D8" s="84" t="str">
+        <x:v>Friends League points formula added</x:v>
+      </x:c>
+      <x:c r="E8" s="84"/>
+      <x:c r="F8" s="4"/>
+      <x:c r="G8" s="4"/>
+      <x:c r="H8" s="4"/>
+      <x:c r="I8" s="4"/>
+      <x:c r="J8" s="4"/>
+      <x:c r="K8" s="4"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="33" t="str">
+        <x:v>Group D</x:v>
+      </x:c>
+      <x:c r="B9" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C9" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D9" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E9" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F9" s="4"/>
+      <x:c r="G9" s="4"/>
+      <x:c r="H9" s="4"/>
+      <x:c r="I9" s="4"/>
+      <x:c r="J9" s="4"/>
+      <x:c r="K9" s="4"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="33" t="str">
+        <x:v>Group E</x:v>
+      </x:c>
+      <x:c r="B10" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C10" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D10" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E10" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F10" s="4"/>
+      <x:c r="G10" s="4"/>
+      <x:c r="H10" s="4"/>
+      <x:c r="I10" s="4"/>
+      <x:c r="J10" s="4"/>
+      <x:c r="K10" s="4"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="33" t="str">
+        <x:v>Group F</x:v>
+      </x:c>
+      <x:c r="B11" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C11" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D11" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E11" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F11" s="4"/>
+      <x:c r="G11" s="4"/>
+      <x:c r="H11" s="4"/>
+      <x:c r="I11" s="4"/>
+      <x:c r="J11" s="4"/>
+      <x:c r="K11" s="4"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="33" t="str">
+        <x:v>Group G</x:v>
+      </x:c>
+      <x:c r="B12" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C12" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D12" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E12" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F12" s="4"/>
+      <x:c r="G12" s="4"/>
+      <x:c r="H12" s="4"/>
+      <x:c r="I12" s="4"/>
+      <x:c r="J12" s="4"/>
+      <x:c r="K12" s="4"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="33" t="str">
+        <x:v>Group H</x:v>
+      </x:c>
+      <x:c r="B13" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C13" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D13" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E13" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F13" s="4"/>
+      <x:c r="G13" s="4"/>
+      <x:c r="H13" s="4"/>
+      <x:c r="I13" s="4"/>
+      <x:c r="J13" s="4"/>
+      <x:c r="K13" s="4"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="33" t="str">
+        <x:v>Group I</x:v>
+      </x:c>
+      <x:c r="B14" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C14" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D14" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E14" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F14" s="4"/>
+      <x:c r="G14" s="4"/>
+      <x:c r="H14" s="4"/>
+      <x:c r="I14" s="4"/>
+      <x:c r="J14" s="4"/>
+      <x:c r="K14" s="4"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="33" t="str">
+        <x:v>Group J</x:v>
+      </x:c>
+      <x:c r="B15" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C15" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D15" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E15" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F15" s="4"/>
+      <x:c r="G15" s="4"/>
+      <x:c r="H15" s="4"/>
+      <x:c r="I15" s="4"/>
+      <x:c r="J15" s="4"/>
+      <x:c r="K15" s="4"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="33" t="str">
+        <x:v>Group K</x:v>
+      </x:c>
+      <x:c r="B16" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D16" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E16" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F16" s="4"/>
+      <x:c r="G16" s="4"/>
+      <x:c r="H16" s="4"/>
+      <x:c r="I16" s="4"/>
+      <x:c r="J16" s="4"/>
+      <x:c r="K16" s="4"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="33" t="str">
+        <x:v>Group L</x:v>
+      </x:c>
+      <x:c r="B17" s="33" t="str">
+        <x:v>4 teams</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="str">
+        <x:v>Track W-D-L, GD, PTS</x:v>
+      </x:c>
+      <x:c r="D17" s="33" t="str">
+        <x:v>Top 2 + selected 3rd-place logic</x:v>
+      </x:c>
+      <x:c r="E17" s="33" t="str">
+        <x:v>Manual buyer input</x:v>
+      </x:c>
+      <x:c r="F17" s="4"/>
+      <x:c r="G17" s="4"/>
+      <x:c r="H17" s="4"/>
+      <x:c r="I17" s="4"/>
+      <x:c r="J17" s="4"/>
+      <x:c r="K17" s="4"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="4"/>
+      <x:c r="B18" s="4"/>
+      <x:c r="C18" s="4"/>
+      <x:c r="D18" s="4"/>
+      <x:c r="E18" s="4"/>
+      <x:c r="F18" s="4"/>
+      <x:c r="G18" s="4"/>
+      <x:c r="H18" s="4"/>
+      <x:c r="I18" s="4"/>
+      <x:c r="J18" s="4"/>
+      <x:c r="K18" s="4"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="4"/>
+      <x:c r="B19" s="4"/>
+      <x:c r="C19" s="4"/>
+      <x:c r="D19" s="4"/>
+      <x:c r="E19" s="4"/>
+      <x:c r="F19" s="4"/>
+      <x:c r="G19" s="4"/>
+      <x:c r="H19" s="4"/>
+      <x:c r="I19" s="4"/>
+      <x:c r="J19" s="4"/>
+      <x:c r="K19" s="4"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="4"/>
+      <x:c r="B20" s="4"/>
+      <x:c r="C20" s="4"/>
+      <x:c r="D20" s="4"/>
+      <x:c r="E20" s="4"/>
+      <x:c r="F20" s="4"/>
+      <x:c r="G20" s="4"/>
+      <x:c r="H20" s="4"/>
+      <x:c r="I20" s="4"/>
+      <x:c r="J20" s="4"/>
+      <x:c r="K20" s="4"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="4"/>
+      <x:c r="B21" s="4"/>
+      <x:c r="C21" s="4"/>
+      <x:c r="D21" s="4"/>
+      <x:c r="E21" s="4"/>
+      <x:c r="F21" s="4"/>
+      <x:c r="G21" s="4"/>
+      <x:c r="H21" s="4"/>
+      <x:c r="I21" s="4"/>
+      <x:c r="J21" s="4"/>
+      <x:c r="K21" s="4"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="60" t="str">
+        <x:v>Knockout Stage</x:v>
+      </x:c>
+      <x:c r="B22" s="60" t="str">
+        <x:v>Match Count</x:v>
+      </x:c>
+      <x:c r="C22" s="60" t="str">
+        <x:v>Output</x:v>
+      </x:c>
+      <x:c r="D22" s="60" t="str">
+        <x:v>Planning Hook</x:v>
+      </x:c>
+      <x:c r="E22" s="4"/>
+      <x:c r="F22" s="4"/>
+      <x:c r="G22" s="4"/>
+      <x:c r="H22" s="4"/>
+      <x:c r="I22" s="4"/>
+      <x:c r="J22" s="4"/>
+      <x:c r="K22" s="4"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="33" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="B23" s="33" t="str">
+        <x:v>16 matches</x:v>
+      </x:c>
+      <x:c r="C23" s="33" t="str">
+        <x:v>Winner advances</x:v>
+      </x:c>
+      <x:c r="D23" s="33" t="str">
+        <x:v>Upset marker + confidence note</x:v>
+      </x:c>
+      <x:c r="E23" s="4"/>
+      <x:c r="F23" s="4"/>
+      <x:c r="G23" s="4"/>
+      <x:c r="H23" s="4"/>
+      <x:c r="I23" s="4"/>
+      <x:c r="J23" s="4"/>
+      <x:c r="K23" s="4"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="33" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="B24" s="33" t="str">
+        <x:v>8 matches</x:v>
+      </x:c>
+      <x:c r="C24" s="33" t="str">
+        <x:v>Winner advances</x:v>
+      </x:c>
+      <x:c r="D24" s="33" t="str">
+        <x:v>Tactical slip comparison</x:v>
+      </x:c>
+      <x:c r="E24" s="4"/>
+      <x:c r="F24" s="4"/>
+      <x:c r="G24" s="4"/>
+      <x:c r="H24" s="4"/>
+      <x:c r="I24" s="4"/>
+      <x:c r="J24" s="4"/>
+      <x:c r="K24" s="4"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="33" t="str">
+        <x:v>Quarterfinal</x:v>
+      </x:c>
+      <x:c r="B25" s="33" t="str">
+        <x:v>4 matches</x:v>
+      </x:c>
+      <x:c r="C25" s="33" t="str">
+        <x:v>Winner advances</x:v>
+      </x:c>
+      <x:c r="D25" s="33" t="str">
+        <x:v>High-stakes watchlist</x:v>
+      </x:c>
+      <x:c r="E25" s="4"/>
+      <x:c r="F25" s="4"/>
+      <x:c r="G25" s="4"/>
+      <x:c r="H25" s="4"/>
+      <x:c r="I25" s="4"/>
+      <x:c r="J25" s="4"/>
+      <x:c r="K25" s="4"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="33" t="str">
+        <x:v>Semifinal</x:v>
+      </x:c>
+      <x:c r="B26" s="33" t="str">
+        <x:v>2 matches</x:v>
+      </x:c>
+      <x:c r="C26" s="33" t="str">
+        <x:v>Winner advances</x:v>
+      </x:c>
+      <x:c r="D26" s="33" t="str">
+        <x:v>Finalist prediction lock</x:v>
+      </x:c>
+      <x:c r="E26" s="4"/>
+      <x:c r="F26" s="4"/>
+      <x:c r="G26" s="4"/>
+      <x:c r="H26" s="4"/>
+      <x:c r="I26" s="4"/>
+      <x:c r="J26" s="4"/>
+      <x:c r="K26" s="4"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="33" t="str">
+        <x:v>Third Place</x:v>
+      </x:c>
+      <x:c r="B27" s="33" t="str">
+        <x:v>1 match</x:v>
+      </x:c>
+      <x:c r="C27" s="33" t="str">
+        <x:v>Optional tracking</x:v>
+      </x:c>
+      <x:c r="D27" s="33" t="str">
+        <x:v>Printable party note</x:v>
+      </x:c>
+      <x:c r="E27" s="4"/>
+      <x:c r="F27" s="4"/>
+      <x:c r="G27" s="4"/>
+      <x:c r="H27" s="4"/>
+      <x:c r="I27" s="4"/>
+      <x:c r="J27" s="4"/>
+      <x:c r="K27" s="4"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="33" t="str">
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="B28" s="33" t="str">
+        <x:v>1 match</x:v>
+      </x:c>
+      <x:c r="C28" s="33" t="str">
+        <x:v>Champion</x:v>
+      </x:c>
+      <x:c r="D28" s="33" t="str">
+        <x:v>Winner/champion generic football cup marker</x:v>
+      </x:c>
+      <x:c r="E28" s="4"/>
+      <x:c r="F28" s="4"/>
+      <x:c r="G28" s="4"/>
+      <x:c r="H28" s="4"/>
+      <x:c r="I28" s="4"/>
+      <x:c r="J28" s="4"/>
+      <x:c r="K28" s="4"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="4"/>
+      <x:c r="B29" s="4"/>
+      <x:c r="C29" s="4"/>
+      <x:c r="D29" s="4"/>
+      <x:c r="E29" s="4"/>
+      <x:c r="F29" s="4"/>
+      <x:c r="G29" s="4"/>
+      <x:c r="H29" s="4"/>
+      <x:c r="I29" s="4"/>
+      <x:c r="J29" s="4"/>
+      <x:c r="K29" s="4"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="4"/>
+      <x:c r="B30" s="4"/>
+      <x:c r="C30" s="4"/>
+      <x:c r="D30" s="4"/>
+      <x:c r="E30" s="4"/>
+      <x:c r="F30" s="4"/>
+      <x:c r="G30" s="4"/>
+      <x:c r="H30" s="4"/>
+      <x:c r="I30" s="4"/>
+      <x:c r="J30" s="4"/>
+      <x:c r="K30" s="4"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="4"/>
+      <x:c r="B31" s="4"/>
+      <x:c r="C31" s="4"/>
+      <x:c r="D31" s="4"/>
+      <x:c r="E31" s="4"/>
+      <x:c r="F31" s="4"/>
+      <x:c r="G31" s="4"/>
+      <x:c r="H31" s="4"/>
+      <x:c r="I31" s="4"/>
+      <x:c r="J31" s="4"/>
+      <x:c r="K31" s="4"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="4"/>
+      <x:c r="B32" s="4"/>
+      <x:c r="C32" s="4"/>
+      <x:c r="D32" s="4"/>
+      <x:c r="E32" s="4"/>
+      <x:c r="F32" s="4"/>
+      <x:c r="G32" s="4"/>
+      <x:c r="H32" s="4"/>
+      <x:c r="I32" s="4"/>
+      <x:c r="J32" s="4"/>
+      <x:c r="K32" s="4"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="4"/>
+      <x:c r="B33" s="4"/>
+      <x:c r="C33" s="4"/>
+      <x:c r="D33" s="4"/>
+      <x:c r="E33" s="4"/>
+      <x:c r="F33" s="4"/>
+      <x:c r="G33" s="4"/>
+      <x:c r="H33" s="4"/>
+      <x:c r="I33" s="4"/>
+      <x:c r="J33" s="4"/>
+      <x:c r="K33" s="4"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="4"/>
+      <x:c r="B34" s="4"/>
+      <x:c r="C34" s="4"/>
+      <x:c r="D34" s="4"/>
+      <x:c r="E34" s="4"/>
+      <x:c r="F34" s="4"/>
+      <x:c r="G34" s="4"/>
+      <x:c r="H34" s="4"/>
+      <x:c r="I34" s="4"/>
+      <x:c r="J34" s="4"/>
+      <x:c r="K34" s="4"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="4"/>
+      <x:c r="B35" s="4"/>
+      <x:c r="C35" s="4"/>
+      <x:c r="D35" s="4"/>
+      <x:c r="E35" s="4"/>
+      <x:c r="F35" s="4"/>
+      <x:c r="G35" s="4"/>
+      <x:c r="H35" s="4"/>
+      <x:c r="I35" s="4"/>
+      <x:c r="J35" s="4"/>
+      <x:c r="K35" s="4"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="4"/>
+      <x:c r="B36" s="4"/>
+      <x:c r="C36" s="4"/>
+      <x:c r="D36" s="4"/>
+      <x:c r="E36" s="4"/>
+      <x:c r="F36" s="4"/>
+      <x:c r="G36" s="4"/>
+      <x:c r="H36" s="4"/>
+      <x:c r="I36" s="4"/>
+      <x:c r="J36" s="4"/>
+      <x:c r="K36" s="4"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="4"/>
+      <x:c r="B37" s="4"/>
+      <x:c r="C37" s="4"/>
+      <x:c r="D37" s="4"/>
+      <x:c r="E37" s="4"/>
+      <x:c r="F37" s="4"/>
+      <x:c r="G37" s="4"/>
+      <x:c r="H37" s="4"/>
+      <x:c r="I37" s="4"/>
+      <x:c r="J37" s="4"/>
+      <x:c r="K37" s="4"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="4"/>
+      <x:c r="B38" s="4"/>
+      <x:c r="C38" s="4"/>
+      <x:c r="D38" s="4"/>
+      <x:c r="E38" s="4"/>
+      <x:c r="F38" s="4"/>
+      <x:c r="G38" s="4"/>
+      <x:c r="H38" s="4"/>
+      <x:c r="I38" s="4"/>
+      <x:c r="J38" s="4"/>
+      <x:c r="K38" s="4"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="4"/>
+      <x:c r="B39" s="4"/>
+      <x:c r="C39" s="4"/>
+      <x:c r="D39" s="4"/>
+      <x:c r="E39" s="4"/>
+      <x:c r="F39" s="4"/>
+      <x:c r="G39" s="4"/>
+      <x:c r="H39" s="4"/>
+      <x:c r="I39" s="4"/>
+      <x:c r="J39" s="4"/>
+      <x:c r="K39" s="4"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="4"/>
+      <x:c r="B40" s="4"/>
+      <x:c r="C40" s="4"/>
+      <x:c r="D40" s="4"/>
+      <x:c r="E40" s="4"/>
+      <x:c r="F40" s="4"/>
+      <x:c r="G40" s="4"/>
+      <x:c r="H40" s="4"/>
+      <x:c r="I40" s="4"/>
+      <x:c r="J40" s="4"/>
+      <x:c r="K40" s="4"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="4"/>
+      <x:c r="B41" s="4"/>
+      <x:c r="C41" s="4"/>
+      <x:c r="D41" s="4"/>
+      <x:c r="E41" s="4"/>
+      <x:c r="F41" s="4"/>
+      <x:c r="G41" s="4"/>
+      <x:c r="H41" s="4"/>
+      <x:c r="I41" s="4"/>
+      <x:c r="J41" s="4"/>
+      <x:c r="K41" s="4"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="4"/>
+      <x:c r="B42" s="4"/>
+      <x:c r="C42" s="4"/>
+      <x:c r="D42" s="4"/>
+      <x:c r="E42" s="4"/>
+      <x:c r="F42" s="4"/>
+      <x:c r="G42" s="4"/>
+      <x:c r="H42" s="4"/>
+      <x:c r="I42" s="4"/>
+      <x:c r="J42" s="4"/>
+      <x:c r="K42" s="4"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="4"/>
+      <x:c r="B43" s="4"/>
+      <x:c r="C43" s="4"/>
+      <x:c r="D43" s="4"/>
+      <x:c r="E43" s="4"/>
+      <x:c r="F43" s="4"/>
+      <x:c r="G43" s="4"/>
+      <x:c r="H43" s="4"/>
+      <x:c r="I43" s="4"/>
+      <x:c r="J43" s="4"/>
+      <x:c r="K43" s="4"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="4"/>
+      <x:c r="B44" s="4"/>
+      <x:c r="C44" s="4"/>
+      <x:c r="D44" s="4"/>
+      <x:c r="E44" s="4"/>
+      <x:c r="F44" s="4"/>
+      <x:c r="G44" s="4"/>
+      <x:c r="H44" s="4"/>
+      <x:c r="I44" s="4"/>
+      <x:c r="J44" s="4"/>
+      <x:c r="K44" s="4"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="4"/>
+      <x:c r="B45" s="4"/>
+      <x:c r="C45" s="4"/>
+      <x:c r="D45" s="4"/>
+      <x:c r="E45" s="4"/>
+      <x:c r="F45" s="4"/>
+      <x:c r="G45" s="4"/>
+      <x:c r="H45" s="4"/>
+      <x:c r="I45" s="4"/>
+      <x:c r="J45" s="4"/>
+      <x:c r="K45" s="4"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="4"/>
+      <x:c r="B46" s="4"/>
+      <x:c r="C46" s="4"/>
+      <x:c r="D46" s="4"/>
+      <x:c r="E46" s="4"/>
+      <x:c r="F46" s="4"/>
+      <x:c r="G46" s="4"/>
+      <x:c r="H46" s="4"/>
+      <x:c r="I46" s="4"/>
+      <x:c r="J46" s="4"/>
+      <x:c r="K46" s="4"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="4"/>
+      <x:c r="B47" s="4"/>
+      <x:c r="C47" s="4"/>
+      <x:c r="D47" s="4"/>
+      <x:c r="E47" s="4"/>
+      <x:c r="F47" s="4"/>
+      <x:c r="G47" s="4"/>
+      <x:c r="H47" s="4"/>
+      <x:c r="I47" s="4"/>
+      <x:c r="J47" s="4"/>
+      <x:c r="K47" s="4"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="4"/>
+      <x:c r="B48" s="4"/>
+      <x:c r="C48" s="4"/>
+      <x:c r="D48" s="4"/>
+      <x:c r="E48" s="4"/>
+      <x:c r="F48" s="4"/>
+      <x:c r="G48" s="4"/>
+      <x:c r="H48" s="4"/>
+      <x:c r="I48" s="4"/>
+      <x:c r="J48" s="4"/>
+      <x:c r="K48" s="4"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="4"/>
+      <x:c r="B49" s="4"/>
+      <x:c r="C49" s="4"/>
+      <x:c r="D49" s="4"/>
+      <x:c r="E49" s="4"/>
+      <x:c r="F49" s="4"/>
+      <x:c r="G49" s="4"/>
+      <x:c r="H49" s="4"/>
+      <x:c r="I49" s="4"/>
+      <x:c r="J49" s="4"/>
+      <x:c r="K49" s="4"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="4"/>
+      <x:c r="B50" s="4"/>
+      <x:c r="C50" s="4"/>
+      <x:c r="D50" s="4"/>
+      <x:c r="E50" s="4"/>
+      <x:c r="F50" s="4"/>
+      <x:c r="G50" s="4"/>
+      <x:c r="H50" s="4"/>
+      <x:c r="I50" s="4"/>
+      <x:c r="J50" s="4"/>
+      <x:c r="K50" s="4"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A2:K2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="2">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R034e034cd03b4ab7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R196cbc8b9c3a482f"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="11" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="13" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="58" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="10" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="71" t="str">
+        <x:v>MATCH PLANNER — 104-MATCH HACKATHON GRID</x:v>
+      </x:c>
+      <x:c r="B1" s="74"/>
+      <x:c r="C1" s="74"/>
+      <x:c r="D1" s="74"/>
+      <x:c r="E1" s="74"/>
+      <x:c r="F1" s="74"/>
+      <x:c r="G1" s="74"/>
+      <x:c r="H1" s="74"/>
+      <x:c r="I1" s="74"/>
+      <x:c r="J1" s="74"/>
+      <x:c r="K1" s="74"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="17" t="str">
+        <x:v>Editable offline match workspace. No official schedule claim; all team slots and results are buyer/demo editable.</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="4" t="str">
+        <x:v>Navigation</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="e">
+        <x:f>HYPERLINK("#'START_HERE'!A1","Back to START")</x:f>
+      </x:c>
+      <x:c r="C3" s="4" t="e">
+        <x:f>HYPERLINK("#'FRIENDS_LEAGUE'!A1","Friends League")</x:f>
+      </x:c>
+      <x:c r="D3" s="4" t="e">
+        <x:f>HYPERLINK("#'AnnexC_495_STATIC'!A1","Annex C")</x:f>
+      </x:c>
+      <x:c r="E3" s="4"/>
+      <x:c r="F3" s="4"/>
+      <x:c r="G3" s="4"/>
+      <x:c r="H3" s="4"/>
+      <x:c r="I3" s="4"/>
+      <x:c r="J3" s="4"/>
+      <x:c r="K3" s="4"/>
+    </x:row>
     <x:row r="4">
       <x:c r="A4" s="4"/>
       <x:c r="B4" s="4"/>
@@ -600,462 +2253,4089 @@
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
     </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="26" t="str">
-        <x:v>Block</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="79" t="str">
+        <x:v>Match ID</x:v>
+      </x:c>
+      <x:c r="B5" s="79" t="str">
+        <x:v>Phase</x:v>
+      </x:c>
+      <x:c r="C5" s="79" t="str">
+        <x:v>Side A</x:v>
+      </x:c>
+      <x:c r="D5" s="79" t="str">
+        <x:v>Side B</x:v>
+      </x:c>
+      <x:c r="E5" s="79" t="str">
+        <x:v>Prediction</x:v>
+      </x:c>
+      <x:c r="F5" s="79" t="str">
+        <x:v>AI Signal</x:v>
+      </x:c>
+      <x:c r="G5" s="79" t="str">
+        <x:v>Confidence %</x:v>
+      </x:c>
+      <x:c r="H5" s="79" t="str">
+        <x:v>Watch Priority</x:v>
+      </x:c>
+      <x:c r="I5" s="79" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
+      <x:c r="J5" s="79" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="K5" s="79" t="str">
+        <x:v>Points</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="84" t="str">
+        <x:v>M001</x:v>
+      </x:c>
+      <x:c r="B6" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C6" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D6" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E6" s="84" t="str"/>
+      <x:c r="F6" s="84" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G6" s="97" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H6" s="84" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I6" s="84" t="str">
+        <x:v>Static planning row for Match 001; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J6" s="90" t="str"/>
+      <x:c r="K6" s="98" t="str">
+        <x:f>IF(J6="","",IF(E6=J6,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="84" t="str">
+        <x:v>M002</x:v>
+      </x:c>
+      <x:c r="B7" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C7" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D7" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E7" s="84" t="str"/>
+      <x:c r="F7" s="84" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G7" s="97" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H7" s="84" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I7" s="84" t="str">
+        <x:v>Static planning row for Match 002; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J7" s="90" t="str"/>
+      <x:c r="K7" s="98" t="str">
+        <x:f>IF(J7="","",IF(E7=J7,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="84" t="str">
+        <x:v>M003</x:v>
+      </x:c>
+      <x:c r="B8" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C8" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D8" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E8" s="84" t="str"/>
+      <x:c r="F8" s="84" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G8" s="97" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H8" s="84" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I8" s="84" t="str">
+        <x:v>Static planning row for Match 003; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J8" s="90" t="str"/>
+      <x:c r="K8" s="98" t="str">
+        <x:f>IF(J8="","",IF(E8=J8,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="84" t="str">
+        <x:v>M004</x:v>
+      </x:c>
+      <x:c r="B9" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C9" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D9" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E9" s="84" t="str"/>
+      <x:c r="F9" s="84" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G9" s="97" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H9" s="84" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I9" s="84" t="str">
+        <x:v>Static planning row for Match 004; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J9" s="90" t="str"/>
+      <x:c r="K9" s="98" t="str">
+        <x:f>IF(J9="","",IF(E9=J9,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="84" t="str">
+        <x:v>M005</x:v>
+      </x:c>
+      <x:c r="B10" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C10" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D10" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E10" s="84" t="str"/>
+      <x:c r="F10" s="84" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G10" s="97" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H10" s="84" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I10" s="84" t="str">
+        <x:v>Static planning row for Match 005; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J10" s="90" t="str"/>
+      <x:c r="K10" s="98" t="str">
+        <x:f>IF(J10="","",IF(E10=J10,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="84" t="str">
+        <x:v>M006</x:v>
+      </x:c>
+      <x:c r="B11" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C11" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D11" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E11" s="84" t="str"/>
+      <x:c r="F11" s="84" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G11" s="97" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H11" s="84" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I11" s="84" t="str">
+        <x:v>Static planning row for Match 006; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J11" s="90" t="str"/>
+      <x:c r="K11" s="98" t="str">
+        <x:f>IF(J11="","",IF(E11=J11,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="84" t="str">
+        <x:v>M007</x:v>
+      </x:c>
+      <x:c r="B12" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C12" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D12" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E12" s="84" t="str"/>
+      <x:c r="F12" s="84" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G12" s="97" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H12" s="84" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I12" s="84" t="str">
+        <x:v>Static planning row for Match 007; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J12" s="90" t="str"/>
+      <x:c r="K12" s="98" t="str">
+        <x:f>IF(J12="","",IF(E12=J12,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="84" t="str">
+        <x:v>M008</x:v>
+      </x:c>
+      <x:c r="B13" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C13" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D13" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E13" s="84" t="str"/>
+      <x:c r="F13" s="84" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G13" s="97" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H13" s="84" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I13" s="84" t="str">
+        <x:v>Static planning row for Match 008; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J13" s="90" t="str"/>
+      <x:c r="K13" s="98" t="str">
+        <x:f>IF(J13="","",IF(E13=J13,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="84" t="str">
+        <x:v>M009</x:v>
+      </x:c>
+      <x:c r="B14" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C14" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D14" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E14" s="84" t="str"/>
+      <x:c r="F14" s="84" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G14" s="97" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H14" s="84" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I14" s="84" t="str">
+        <x:v>Static planning row for Match 009; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J14" s="90" t="str"/>
+      <x:c r="K14" s="98" t="str">
+        <x:f>IF(J14="","",IF(E14=J14,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="84" t="str">
+        <x:v>M010</x:v>
+      </x:c>
+      <x:c r="B15" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C15" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D15" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E15" s="84" t="str"/>
+      <x:c r="F15" s="84" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G15" s="97" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H15" s="84" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I15" s="84" t="str">
+        <x:v>Static planning row for Match 010; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J15" s="90" t="str"/>
+      <x:c r="K15" s="98" t="str">
+        <x:f>IF(J15="","",IF(E15=J15,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="84" t="str">
+        <x:v>M011</x:v>
+      </x:c>
+      <x:c r="B16" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C16" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D16" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E16" s="84" t="str"/>
+      <x:c r="F16" s="84" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G16" s="97" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H16" s="84" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I16" s="84" t="str">
+        <x:v>Static planning row for Match 011; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J16" s="90" t="str"/>
+      <x:c r="K16" s="98" t="str">
+        <x:f>IF(J16="","",IF(E16=J16,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="84" t="str">
+        <x:v>M012</x:v>
+      </x:c>
+      <x:c r="B17" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C17" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D17" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E17" s="84" t="str"/>
+      <x:c r="F17" s="84" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G17" s="97" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H17" s="84" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I17" s="84" t="str">
+        <x:v>Static planning row for Match 012; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J17" s="90" t="str"/>
+      <x:c r="K17" s="98" t="str">
+        <x:f>IF(J17="","",IF(E17=J17,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="84" t="str">
+        <x:v>M013</x:v>
+      </x:c>
+      <x:c r="B18" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C18" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D18" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E18" s="84" t="str"/>
+      <x:c r="F18" s="84" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G18" s="97" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H18" s="84" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I18" s="84" t="str">
+        <x:v>Static planning row for Match 013; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J18" s="90" t="str"/>
+      <x:c r="K18" s="98" t="str">
+        <x:f>IF(J18="","",IF(E18=J18,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="84" t="str">
+        <x:v>M014</x:v>
+      </x:c>
+      <x:c r="B19" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C19" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D19" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E19" s="84" t="str"/>
+      <x:c r="F19" s="84" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G19" s="97" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H19" s="84" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I19" s="84" t="str">
+        <x:v>Static planning row for Match 014; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J19" s="90" t="str"/>
+      <x:c r="K19" s="98" t="str">
+        <x:f>IF(J19="","",IF(E19=J19,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="84" t="str">
+        <x:v>M015</x:v>
+      </x:c>
+      <x:c r="B20" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C20" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D20" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E20" s="84" t="str"/>
+      <x:c r="F20" s="84" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G20" s="97" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H20" s="84" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I20" s="84" t="str">
+        <x:v>Static planning row for Match 015; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J20" s="90" t="str"/>
+      <x:c r="K20" s="98" t="str">
+        <x:f>IF(J20="","",IF(E20=J20,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="84" t="str">
+        <x:v>M016</x:v>
+      </x:c>
+      <x:c r="B21" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C21" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D21" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E21" s="84" t="str"/>
+      <x:c r="F21" s="84" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G21" s="97" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H21" s="84" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I21" s="84" t="str">
+        <x:v>Static planning row for Match 016; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J21" s="90" t="str"/>
+      <x:c r="K21" s="98" t="str">
+        <x:f>IF(J21="","",IF(E21=J21,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="22">
+      <x:c r="A22" s="84" t="str">
+        <x:v>M017</x:v>
+      </x:c>
+      <x:c r="B22" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C22" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D22" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E22" s="84" t="str"/>
+      <x:c r="F22" s="84" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G22" s="97" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H22" s="84" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I22" s="84" t="str">
+        <x:v>Static planning row for Match 017; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J22" s="90" t="str"/>
+      <x:c r="K22" s="98" t="str">
+        <x:f>IF(J22="","",IF(E22=J22,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="23">
+      <x:c r="A23" s="84" t="str">
+        <x:v>M018</x:v>
+      </x:c>
+      <x:c r="B23" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C23" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D23" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E23" s="84" t="str"/>
+      <x:c r="F23" s="84" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G23" s="97" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H23" s="84" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I23" s="84" t="str">
+        <x:v>Static planning row for Match 018; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J23" s="90" t="str"/>
+      <x:c r="K23" s="98" t="str">
+        <x:f>IF(J23="","",IF(E23=J23,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="24">
+      <x:c r="A24" s="84" t="str">
+        <x:v>M019</x:v>
+      </x:c>
+      <x:c r="B24" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C24" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D24" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E24" s="84" t="str"/>
+      <x:c r="F24" s="84" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G24" s="97" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H24" s="84" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I24" s="84" t="str">
+        <x:v>Static planning row for Match 019; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J24" s="90" t="str"/>
+      <x:c r="K24" s="98" t="str">
+        <x:f>IF(J24="","",IF(E24=J24,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="25">
+      <x:c r="A25" s="84" t="str">
+        <x:v>M020</x:v>
+      </x:c>
+      <x:c r="B25" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C25" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D25" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E25" s="84" t="str"/>
+      <x:c r="F25" s="84" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G25" s="97" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H25" s="84" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I25" s="84" t="str">
+        <x:v>Static planning row for Match 020; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J25" s="90" t="str"/>
+      <x:c r="K25" s="98" t="str">
+        <x:f>IF(J25="","",IF(E25=J25,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="26">
+      <x:c r="A26" s="84" t="str">
+        <x:v>M021</x:v>
+      </x:c>
+      <x:c r="B26" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C26" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D26" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E26" s="84" t="str"/>
+      <x:c r="F26" s="84" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G26" s="97" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H26" s="84" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I26" s="84" t="str">
+        <x:v>Static planning row for Match 021; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J26" s="90" t="str"/>
+      <x:c r="K26" s="98" t="str">
+        <x:f>IF(J26="","",IF(E26=J26,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" s="84" t="str">
+        <x:v>M022</x:v>
+      </x:c>
+      <x:c r="B27" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C27" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D27" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E27" s="84" t="str"/>
+      <x:c r="F27" s="84" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G27" s="97" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H27" s="84" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I27" s="84" t="str">
+        <x:v>Static planning row for Match 022; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J27" s="90" t="str"/>
+      <x:c r="K27" s="98" t="str">
+        <x:f>IF(J27="","",IF(E27=J27,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="A28" s="84" t="str">
+        <x:v>M023</x:v>
+      </x:c>
+      <x:c r="B28" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C28" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D28" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E28" s="84" t="str"/>
+      <x:c r="F28" s="84" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G28" s="97" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H28" s="84" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I28" s="84" t="str">
+        <x:v>Static planning row for Match 023; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J28" s="90" t="str"/>
+      <x:c r="K28" s="98" t="str">
+        <x:f>IF(J28="","",IF(E28=J28,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="29">
+      <x:c r="A29" s="84" t="str">
+        <x:v>M024</x:v>
+      </x:c>
+      <x:c r="B29" s="84" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C29" s="84" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D29" s="84" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E29" s="84" t="str"/>
+      <x:c r="F29" s="84" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G29" s="97" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H29" s="84" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I29" s="84" t="str">
+        <x:v>Static planning row for Match 024; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J29" s="90" t="str"/>
+      <x:c r="K29" s="98" t="str">
+        <x:f>IF(J29="","",IF(E29=J29,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="30">
+      <x:c r="A30" s="90" t="str">
+        <x:v>M025</x:v>
+      </x:c>
+      <x:c r="B30" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C30" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D30" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E30" s="90" t="str"/>
+      <x:c r="F30" s="90" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G30" s="98" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H30" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I30" s="90" t="str">
+        <x:v>Static planning row for Match 025; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J30" s="90" t="str"/>
+      <x:c r="K30" s="98" t="str">
+        <x:f>IF(J30="","",IF(E30=J30,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="31">
+      <x:c r="A31" s="90" t="str">
+        <x:v>M026</x:v>
+      </x:c>
+      <x:c r="B31" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C31" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D31" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E31" s="90" t="str"/>
+      <x:c r="F31" s="90" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G31" s="98" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H31" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I31" s="90" t="str">
+        <x:v>Static planning row for Match 026; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J31" s="90" t="str"/>
+      <x:c r="K31" s="98" t="str">
+        <x:f>IF(J31="","",IF(E31=J31,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="32">
+      <x:c r="A32" s="90" t="str">
+        <x:v>M027</x:v>
+      </x:c>
+      <x:c r="B32" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C32" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D32" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E32" s="90" t="str"/>
+      <x:c r="F32" s="90" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G32" s="98" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H32" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I32" s="90" t="str">
+        <x:v>Static planning row for Match 027; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J32" s="90" t="str"/>
+      <x:c r="K32" s="98" t="str">
+        <x:f>IF(J32="","",IF(E32=J32,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="33">
+      <x:c r="A33" s="90" t="str">
+        <x:v>M028</x:v>
+      </x:c>
+      <x:c r="B33" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C33" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D33" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E33" s="90" t="str"/>
+      <x:c r="F33" s="90" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G33" s="98" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H33" s="90" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I33" s="90" t="str">
+        <x:v>Static planning row for Match 028; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J33" s="90" t="str"/>
+      <x:c r="K33" s="98" t="str">
+        <x:f>IF(J33="","",IF(E33=J33,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" s="90" t="str">
+        <x:v>M029</x:v>
+      </x:c>
+      <x:c r="B34" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C34" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D34" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E34" s="90" t="str"/>
+      <x:c r="F34" s="90" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G34" s="98" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H34" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I34" s="90" t="str">
+        <x:v>Static planning row for Match 029; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J34" s="90" t="str"/>
+      <x:c r="K34" s="98" t="str">
+        <x:f>IF(J34="","",IF(E34=J34,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="35">
+      <x:c r="A35" s="90" t="str">
+        <x:v>M030</x:v>
+      </x:c>
+      <x:c r="B35" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C35" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D35" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E35" s="90" t="str"/>
+      <x:c r="F35" s="90" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G35" s="98" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H35" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I35" s="90" t="str">
+        <x:v>Static planning row for Match 030; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J35" s="90" t="str"/>
+      <x:c r="K35" s="98" t="str">
+        <x:f>IF(J35="","",IF(E35=J35,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="36">
+      <x:c r="A36" s="90" t="str">
+        <x:v>M031</x:v>
+      </x:c>
+      <x:c r="B36" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C36" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D36" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E36" s="90" t="str"/>
+      <x:c r="F36" s="90" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G36" s="98" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H36" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I36" s="90" t="str">
+        <x:v>Static planning row for Match 031; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J36" s="90" t="str"/>
+      <x:c r="K36" s="98" t="str">
+        <x:f>IF(J36="","",IF(E36=J36,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="90" t="str">
+        <x:v>M032</x:v>
+      </x:c>
+      <x:c r="B37" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C37" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D37" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E37" s="90" t="str"/>
+      <x:c r="F37" s="90" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G37" s="98" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H37" s="90" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I37" s="90" t="str">
+        <x:v>Static planning row for Match 032; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J37" s="90" t="str"/>
+      <x:c r="K37" s="98" t="str">
+        <x:f>IF(J37="","",IF(E37=J37,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="38">
+      <x:c r="A38" s="90" t="str">
+        <x:v>M033</x:v>
+      </x:c>
+      <x:c r="B38" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C38" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D38" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E38" s="90" t="str"/>
+      <x:c r="F38" s="90" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G38" s="98" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H38" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I38" s="90" t="str">
+        <x:v>Static planning row for Match 033; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J38" s="90" t="str"/>
+      <x:c r="K38" s="98" t="str">
+        <x:f>IF(J38="","",IF(E38=J38,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="39">
+      <x:c r="A39" s="90" t="str">
+        <x:v>M034</x:v>
+      </x:c>
+      <x:c r="B39" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C39" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D39" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E39" s="90" t="str"/>
+      <x:c r="F39" s="90" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G39" s="98" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H39" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I39" s="90" t="str">
+        <x:v>Static planning row for Match 034; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J39" s="90" t="str"/>
+      <x:c r="K39" s="98" t="str">
+        <x:f>IF(J39="","",IF(E39=J39,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="40">
+      <x:c r="A40" s="90" t="str">
+        <x:v>M035</x:v>
+      </x:c>
+      <x:c r="B40" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C40" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D40" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E40" s="90" t="str"/>
+      <x:c r="F40" s="90" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G40" s="98" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H40" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I40" s="90" t="str">
+        <x:v>Static planning row for Match 035; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J40" s="90" t="str"/>
+      <x:c r="K40" s="98" t="str">
+        <x:f>IF(J40="","",IF(E40=J40,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="41">
+      <x:c r="A41" s="90" t="str">
+        <x:v>M036</x:v>
+      </x:c>
+      <x:c r="B41" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C41" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D41" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E41" s="90" t="str"/>
+      <x:c r="F41" s="90" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G41" s="98" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H41" s="90" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I41" s="90" t="str">
+        <x:v>Static planning row for Match 036; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J41" s="90" t="str"/>
+      <x:c r="K41" s="98" t="str">
+        <x:f>IF(J41="","",IF(E41=J41,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="42">
+      <x:c r="A42" s="90" t="str">
+        <x:v>M037</x:v>
+      </x:c>
+      <x:c r="B42" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C42" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D42" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E42" s="90" t="str"/>
+      <x:c r="F42" s="90" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G42" s="98" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H42" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I42" s="90" t="str">
+        <x:v>Static planning row for Match 037; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J42" s="90" t="str"/>
+      <x:c r="K42" s="98" t="str">
+        <x:f>IF(J42="","",IF(E42=J42,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="43">
+      <x:c r="A43" s="90" t="str">
+        <x:v>M038</x:v>
+      </x:c>
+      <x:c r="B43" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C43" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D43" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E43" s="90" t="str"/>
+      <x:c r="F43" s="90" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G43" s="98" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H43" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I43" s="90" t="str">
+        <x:v>Static planning row for Match 038; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J43" s="90" t="str"/>
+      <x:c r="K43" s="98" t="str">
+        <x:f>IF(J43="","",IF(E43=J43,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="44">
+      <x:c r="A44" s="90" t="str">
+        <x:v>M039</x:v>
+      </x:c>
+      <x:c r="B44" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C44" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D44" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E44" s="90" t="str"/>
+      <x:c r="F44" s="90" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G44" s="98" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H44" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I44" s="90" t="str">
+        <x:v>Static planning row for Match 039; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J44" s="90" t="str"/>
+      <x:c r="K44" s="98" t="str">
+        <x:f>IF(J44="","",IF(E44=J44,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="45">
+      <x:c r="A45" s="90" t="str">
+        <x:v>M040</x:v>
+      </x:c>
+      <x:c r="B45" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C45" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D45" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E45" s="90" t="str"/>
+      <x:c r="F45" s="90" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G45" s="98" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H45" s="90" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I45" s="90" t="str">
+        <x:v>Static planning row for Match 040; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J45" s="90" t="str"/>
+      <x:c r="K45" s="98" t="str">
+        <x:f>IF(J45="","",IF(E45=J45,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="46">
+      <x:c r="A46" s="90" t="str">
+        <x:v>M041</x:v>
+      </x:c>
+      <x:c r="B46" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C46" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D46" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E46" s="90" t="str"/>
+      <x:c r="F46" s="90" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G46" s="98" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H46" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I46" s="90" t="str">
+        <x:v>Static planning row for Match 041; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J46" s="90" t="str"/>
+      <x:c r="K46" s="98" t="str">
+        <x:f>IF(J46="","",IF(E46=J46,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="47">
+      <x:c r="A47" s="90" t="str">
+        <x:v>M042</x:v>
+      </x:c>
+      <x:c r="B47" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C47" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D47" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E47" s="90" t="str"/>
+      <x:c r="F47" s="90" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G47" s="98" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H47" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I47" s="90" t="str">
+        <x:v>Static planning row for Match 042; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J47" s="90" t="str"/>
+      <x:c r="K47" s="98" t="str">
+        <x:f>IF(J47="","",IF(E47=J47,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="48">
+      <x:c r="A48" s="90" t="str">
+        <x:v>M043</x:v>
+      </x:c>
+      <x:c r="B48" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C48" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D48" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E48" s="90" t="str"/>
+      <x:c r="F48" s="90" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G48" s="98" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H48" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I48" s="90" t="str">
+        <x:v>Static planning row for Match 043; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J48" s="90" t="str"/>
+      <x:c r="K48" s="98" t="str">
+        <x:f>IF(J48="","",IF(E48=J48,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="49">
+      <x:c r="A49" s="90" t="str">
+        <x:v>M044</x:v>
+      </x:c>
+      <x:c r="B49" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C49" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D49" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E49" s="90" t="str"/>
+      <x:c r="F49" s="90" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G49" s="98" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H49" s="90" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I49" s="90" t="str">
+        <x:v>Static planning row for Match 044; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J49" s="90" t="str"/>
+      <x:c r="K49" s="98" t="str">
+        <x:f>IF(J49="","",IF(E49=J49,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="50">
+      <x:c r="A50" s="90" t="str">
+        <x:v>M045</x:v>
+      </x:c>
+      <x:c r="B50" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C50" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D50" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E50" s="90" t="str"/>
+      <x:c r="F50" s="90" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G50" s="98" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H50" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I50" s="90" t="str">
+        <x:v>Static planning row for Match 045; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J50" s="90" t="str"/>
+      <x:c r="K50" s="98" t="str">
+        <x:f>IF(J50="","",IF(E50=J50,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="51">
+      <x:c r="A51" s="90" t="str">
+        <x:v>M046</x:v>
+      </x:c>
+      <x:c r="B51" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C51" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D51" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E51" s="90" t="str"/>
+      <x:c r="F51" s="90" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G51" s="98" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H51" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I51" s="90" t="str">
+        <x:v>Static planning row for Match 046; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J51" s="90" t="str"/>
+      <x:c r="K51" s="98" t="str">
+        <x:f>IF(J51="","",IF(E51=J51,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="52">
+      <x:c r="A52" s="90" t="str">
+        <x:v>M047</x:v>
+      </x:c>
+      <x:c r="B52" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C52" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D52" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E52" s="90" t="str"/>
+      <x:c r="F52" s="90" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G52" s="98" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H52" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I52" s="90" t="str">
+        <x:v>Static planning row for Match 047; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J52" s="90" t="str"/>
+      <x:c r="K52" s="98" t="str">
+        <x:f>IF(J52="","",IF(E52=J52,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="53">
+      <x:c r="A53" s="90" t="str">
+        <x:v>M048</x:v>
+      </x:c>
+      <x:c r="B53" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C53" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D53" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E53" s="90" t="str"/>
+      <x:c r="F53" s="90" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G53" s="98" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H53" s="90" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I53" s="90" t="str">
+        <x:v>Static planning row for Match 048; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J53" s="90" t="str"/>
+      <x:c r="K53" s="98" t="str">
+        <x:f>IF(J53="","",IF(E53=J53,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" s="90" t="str">
+        <x:v>M049</x:v>
+      </x:c>
+      <x:c r="B54" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C54" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D54" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E54" s="90" t="str"/>
+      <x:c r="F54" s="90" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G54" s="98" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H54" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I54" s="90" t="str">
+        <x:v>Static planning row for Match 049; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J54" s="90" t="str"/>
+      <x:c r="K54" s="98" t="str">
+        <x:f>IF(J54="","",IF(E54=J54,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" s="90" t="str">
+        <x:v>M050</x:v>
+      </x:c>
+      <x:c r="B55" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C55" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D55" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E55" s="90" t="str"/>
+      <x:c r="F55" s="90" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G55" s="98" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H55" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I55" s="90" t="str">
+        <x:v>Static planning row for Match 050; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J55" s="90" t="str"/>
+      <x:c r="K55" s="98" t="str">
+        <x:f>IF(J55="","",IF(E55=J55,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" s="90" t="str">
+        <x:v>M051</x:v>
+      </x:c>
+      <x:c r="B56" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C56" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D56" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E56" s="90" t="str"/>
+      <x:c r="F56" s="90" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G56" s="98" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H56" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I56" s="90" t="str">
+        <x:v>Static planning row for Match 051; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J56" s="90" t="str"/>
+      <x:c r="K56" s="98" t="str">
+        <x:f>IF(J56="","",IF(E56=J56,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="90" t="str">
+        <x:v>M052</x:v>
+      </x:c>
+      <x:c r="B57" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C57" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D57" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E57" s="90" t="str"/>
+      <x:c r="F57" s="90" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G57" s="98" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H57" s="90" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I57" s="90" t="str">
+        <x:v>Static planning row for Match 052; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J57" s="90" t="str"/>
+      <x:c r="K57" s="98" t="str">
+        <x:f>IF(J57="","",IF(E57=J57,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="90" t="str">
+        <x:v>M053</x:v>
+      </x:c>
+      <x:c r="B58" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C58" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D58" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E58" s="90" t="str"/>
+      <x:c r="F58" s="90" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G58" s="98" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H58" s="90" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I58" s="90" t="str">
+        <x:v>Static planning row for Match 053; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J58" s="90" t="str"/>
+      <x:c r="K58" s="98" t="str">
+        <x:f>IF(J58="","",IF(E58=J58,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="90" t="str">
+        <x:v>M054</x:v>
+      </x:c>
+      <x:c r="B59" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C59" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D59" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E59" s="90" t="str"/>
+      <x:c r="F59" s="90" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G59" s="98" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H59" s="90" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I59" s="90" t="str">
+        <x:v>Static planning row for Match 054; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J59" s="90" t="str"/>
+      <x:c r="K59" s="98" t="str">
+        <x:f>IF(J59="","",IF(E59=J59,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="90" t="str">
+        <x:v>M055</x:v>
+      </x:c>
+      <x:c r="B60" s="90" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C60" s="90" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D60" s="90" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E60" s="90" t="str"/>
+      <x:c r="F60" s="90" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G60" s="98" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H60" s="90" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I60" s="90" t="str">
+        <x:v>Static planning row for Match 055; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J60" s="90" t="str"/>
+      <x:c r="K60" s="98" t="str">
+        <x:f>IF(J60="","",IF(E60=J60,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="96" t="str">
+        <x:v>M056</x:v>
+      </x:c>
+      <x:c r="B61" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C61" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D61" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E61" s="96" t="str"/>
+      <x:c r="F61" s="96" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G61" s="99" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H61" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I61" s="96" t="str">
+        <x:v>Static planning row for Match 056; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J61" s="96" t="str"/>
+      <x:c r="K61" s="99" t="str">
+        <x:f>IF(J61="","",IF(E61=J61,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="96" t="str">
+        <x:v>M057</x:v>
+      </x:c>
+      <x:c r="B62" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C62" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D62" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E62" s="96" t="str"/>
+      <x:c r="F62" s="96" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G62" s="99" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H62" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I62" s="96" t="str">
+        <x:v>Static planning row for Match 057; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J62" s="96" t="str"/>
+      <x:c r="K62" s="99" t="str">
+        <x:f>IF(J62="","",IF(E62=J62,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="96" t="str">
+        <x:v>M058</x:v>
+      </x:c>
+      <x:c r="B63" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C63" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D63" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E63" s="96" t="str"/>
+      <x:c r="F63" s="96" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G63" s="99" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H63" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I63" s="96" t="str">
+        <x:v>Static planning row for Match 058; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J63" s="96" t="str"/>
+      <x:c r="K63" s="99" t="str">
+        <x:f>IF(J63="","",IF(E63=J63,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="96" t="str">
+        <x:v>M059</x:v>
+      </x:c>
+      <x:c r="B64" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C64" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D64" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E64" s="96" t="str"/>
+      <x:c r="F64" s="96" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G64" s="99" t="n">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="H64" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I64" s="96" t="str">
+        <x:v>Static planning row for Match 059; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J64" s="96" t="str"/>
+      <x:c r="K64" s="99" t="str">
+        <x:f>IF(J64="","",IF(E64=J64,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="96" t="str">
+        <x:v>M060</x:v>
+      </x:c>
+      <x:c r="B65" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C65" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D65" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E65" s="96" t="str"/>
+      <x:c r="F65" s="96" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G65" s="99" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H65" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I65" s="96" t="str">
+        <x:v>Static planning row for Match 060; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J65" s="96" t="str"/>
+      <x:c r="K65" s="99" t="str">
+        <x:f>IF(J65="","",IF(E65=J65,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="96" t="str">
+        <x:v>M061</x:v>
+      </x:c>
+      <x:c r="B66" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C66" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D66" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E66" s="96" t="str"/>
+      <x:c r="F66" s="96" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G66" s="99" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H66" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I66" s="96" t="str">
+        <x:v>Static planning row for Match 061; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J66" s="96" t="str"/>
+      <x:c r="K66" s="99" t="str">
+        <x:f>IF(J66="","",IF(E66=J66,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="96" t="str">
+        <x:v>M062</x:v>
+      </x:c>
+      <x:c r="B67" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C67" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D67" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E67" s="96" t="str"/>
+      <x:c r="F67" s="96" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G67" s="99" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H67" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I67" s="96" t="str">
+        <x:v>Static planning row for Match 062; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J67" s="96" t="str"/>
+      <x:c r="K67" s="99" t="str">
+        <x:f>IF(J67="","",IF(E67=J67,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="96" t="str">
+        <x:v>M063</x:v>
+      </x:c>
+      <x:c r="B68" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C68" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D68" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E68" s="96" t="str"/>
+      <x:c r="F68" s="96" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G68" s="99" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H68" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I68" s="96" t="str">
+        <x:v>Static planning row for Match 063; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J68" s="96" t="str"/>
+      <x:c r="K68" s="99" t="str">
+        <x:f>IF(J68="","",IF(E68=J68,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="96" t="str">
+        <x:v>M064</x:v>
+      </x:c>
+      <x:c r="B69" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C69" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D69" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E69" s="96" t="str"/>
+      <x:c r="F69" s="96" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G69" s="99" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H69" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I69" s="96" t="str">
+        <x:v>Static planning row for Match 064; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J69" s="96" t="str"/>
+      <x:c r="K69" s="99" t="str">
+        <x:f>IF(J69="","",IF(E69=J69,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="96" t="str">
+        <x:v>M065</x:v>
+      </x:c>
+      <x:c r="B70" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C70" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D70" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E70" s="96" t="str"/>
+      <x:c r="F70" s="96" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G70" s="99" t="n">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="H70" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I70" s="96" t="str">
+        <x:v>Static planning row for Match 065; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J70" s="96" t="str"/>
+      <x:c r="K70" s="99" t="str">
+        <x:f>IF(J70="","",IF(E70=J70,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" s="96" t="str">
+        <x:v>M066</x:v>
+      </x:c>
+      <x:c r="B71" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C71" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D71" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E71" s="96" t="str"/>
+      <x:c r="F71" s="96" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G71" s="99" t="n">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="H71" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I71" s="96" t="str">
+        <x:v>Static planning row for Match 066; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J71" s="96" t="str"/>
+      <x:c r="K71" s="99" t="str">
+        <x:f>IF(J71="","",IF(E71=J71,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" s="96" t="str">
+        <x:v>M067</x:v>
+      </x:c>
+      <x:c r="B72" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C72" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D72" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E72" s="96" t="str"/>
+      <x:c r="F72" s="96" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G72" s="99" t="n">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="H72" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I72" s="96" t="str">
+        <x:v>Static planning row for Match 067; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J72" s="96" t="str"/>
+      <x:c r="K72" s="99" t="str">
+        <x:f>IF(J72="","",IF(E72=J72,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" s="96" t="str">
+        <x:v>M068</x:v>
+      </x:c>
+      <x:c r="B73" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C73" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D73" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E73" s="96" t="str"/>
+      <x:c r="F73" s="96" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G73" s="99" t="n">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H73" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I73" s="96" t="str">
+        <x:v>Static planning row for Match 068; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J73" s="96" t="str"/>
+      <x:c r="K73" s="99" t="str">
+        <x:f>IF(J73="","",IF(E73=J73,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" s="96" t="str">
+        <x:v>M069</x:v>
+      </x:c>
+      <x:c r="B74" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C74" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D74" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E74" s="96" t="str"/>
+      <x:c r="F74" s="96" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G74" s="99" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H74" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I74" s="96" t="str">
+        <x:v>Static planning row for Match 069; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J74" s="96" t="str"/>
+      <x:c r="K74" s="99" t="str">
+        <x:f>IF(J74="","",IF(E74=J74,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" s="96" t="str">
+        <x:v>M070</x:v>
+      </x:c>
+      <x:c r="B75" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C75" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D75" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E75" s="96" t="str"/>
+      <x:c r="F75" s="96" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G75" s="99" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="H75" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I75" s="96" t="str">
+        <x:v>Static planning row for Match 070; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J75" s="96" t="str"/>
+      <x:c r="K75" s="99" t="str">
+        <x:f>IF(J75="","",IF(E75=J75,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" s="96" t="str">
+        <x:v>M071</x:v>
+      </x:c>
+      <x:c r="B76" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C76" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D76" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E76" s="96" t="str"/>
+      <x:c r="F76" s="96" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G76" s="99" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H76" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I76" s="96" t="str">
+        <x:v>Static planning row for Match 071; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J76" s="96" t="str"/>
+      <x:c r="K76" s="99" t="str">
+        <x:f>IF(J76="","",IF(E76=J76,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" s="96" t="str">
+        <x:v>M072</x:v>
+      </x:c>
+      <x:c r="B77" s="96" t="str">
+        <x:v>Group Stage</x:v>
+      </x:c>
+      <x:c r="C77" s="96" t="str">
+        <x:v>Group Stage Side A</x:v>
+      </x:c>
+      <x:c r="D77" s="96" t="str">
+        <x:v>Group Stage Side B</x:v>
+      </x:c>
+      <x:c r="E77" s="96" t="str"/>
+      <x:c r="F77" s="96" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G77" s="99" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="H77" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I77" s="96" t="str">
+        <x:v>Static planning row for Match 072; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J77" s="96" t="str"/>
+      <x:c r="K77" s="99" t="str">
+        <x:f>IF(J77="","",IF(E77=J77,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" s="96" t="str">
+        <x:v>M073</x:v>
+      </x:c>
+      <x:c r="B78" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C78" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D78" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E78" s="96" t="str"/>
+      <x:c r="F78" s="96" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G78" s="99" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H78" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I78" s="96" t="str">
+        <x:v>Static planning row for Match 073; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J78" s="96" t="str"/>
+      <x:c r="K78" s="99" t="str">
+        <x:f>IF(J78="","",IF(E78=J78,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" s="96" t="str">
+        <x:v>M074</x:v>
+      </x:c>
+      <x:c r="B79" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C79" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D79" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E79" s="96" t="str"/>
+      <x:c r="F79" s="96" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G79" s="99" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="H79" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I79" s="96" t="str">
+        <x:v>Static planning row for Match 074; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J79" s="96" t="str"/>
+      <x:c r="K79" s="99" t="str">
+        <x:f>IF(J79="","",IF(E79=J79,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" s="96" t="str">
+        <x:v>M075</x:v>
+      </x:c>
+      <x:c r="B80" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C80" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D80" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E80" s="96" t="str"/>
+      <x:c r="F80" s="96" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G80" s="99" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H80" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I80" s="96" t="str">
+        <x:v>Static planning row for Match 075; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J80" s="96" t="str"/>
+      <x:c r="K80" s="99" t="str">
+        <x:f>IF(J80="","",IF(E80=J80,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" s="96" t="str">
+        <x:v>M076</x:v>
+      </x:c>
+      <x:c r="B81" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C81" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D81" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E81" s="96" t="str"/>
+      <x:c r="F81" s="96" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G81" s="99" t="n">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="H81" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I81" s="96" t="str">
+        <x:v>Static planning row for Match 076; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J81" s="96" t="str"/>
+      <x:c r="K81" s="99" t="str">
+        <x:f>IF(J81="","",IF(E81=J81,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" s="96" t="str">
+        <x:v>M077</x:v>
+      </x:c>
+      <x:c r="B82" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C82" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D82" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E82" s="96" t="str"/>
+      <x:c r="F82" s="96" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G82" s="99" t="n">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H82" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I82" s="96" t="str">
+        <x:v>Static planning row for Match 077; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J82" s="96" t="str"/>
+      <x:c r="K82" s="99" t="str">
+        <x:f>IF(J82="","",IF(E82=J82,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" s="96" t="str">
+        <x:v>M078</x:v>
+      </x:c>
+      <x:c r="B83" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C83" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D83" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E83" s="96" t="str"/>
+      <x:c r="F83" s="96" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G83" s="99" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H83" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I83" s="96" t="str">
+        <x:v>Static planning row for Match 078; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J83" s="96" t="str"/>
+      <x:c r="K83" s="99" t="str">
+        <x:f>IF(J83="","",IF(E83=J83,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" s="96" t="str">
+        <x:v>M079</x:v>
+      </x:c>
+      <x:c r="B84" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C84" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D84" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E84" s="96" t="str"/>
+      <x:c r="F84" s="96" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G84" s="99" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H84" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I84" s="96" t="str">
+        <x:v>Static planning row for Match 079; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J84" s="96" t="str"/>
+      <x:c r="K84" s="99" t="str">
+        <x:f>IF(J84="","",IF(E84=J84,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" s="96" t="str">
+        <x:v>M080</x:v>
+      </x:c>
+      <x:c r="B85" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C85" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D85" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E85" s="96" t="str"/>
+      <x:c r="F85" s="96" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G85" s="99" t="n">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="H85" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I85" s="96" t="str">
+        <x:v>Static planning row for Match 080; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J85" s="96" t="str"/>
+      <x:c r="K85" s="99" t="str">
+        <x:f>IF(J85="","",IF(E85=J85,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" s="96" t="str">
+        <x:v>M081</x:v>
+      </x:c>
+      <x:c r="B86" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C86" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D86" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E86" s="96" t="str"/>
+      <x:c r="F86" s="96" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G86" s="99" t="n">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H86" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I86" s="96" t="str">
+        <x:v>Static planning row for Match 081; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J86" s="96" t="str"/>
+      <x:c r="K86" s="99" t="str">
+        <x:f>IF(J86="","",IF(E86=J86,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" s="96" t="str">
+        <x:v>M082</x:v>
+      </x:c>
+      <x:c r="B87" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C87" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D87" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E87" s="96" t="str"/>
+      <x:c r="F87" s="96" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G87" s="99" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H87" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I87" s="96" t="str">
+        <x:v>Static planning row for Match 082; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J87" s="96" t="str"/>
+      <x:c r="K87" s="99" t="str">
+        <x:f>IF(J87="","",IF(E87=J87,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" s="96" t="str">
+        <x:v>M083</x:v>
+      </x:c>
+      <x:c r="B88" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C88" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D88" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E88" s="96" t="str"/>
+      <x:c r="F88" s="96" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G88" s="99" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H88" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I88" s="96" t="str">
+        <x:v>Static planning row for Match 083; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J88" s="96" t="str"/>
+      <x:c r="K88" s="99" t="str">
+        <x:f>IF(J88="","",IF(E88=J88,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" s="96" t="str">
+        <x:v>M084</x:v>
+      </x:c>
+      <x:c r="B89" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C89" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D89" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E89" s="96" t="str"/>
+      <x:c r="F89" s="96" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G89" s="99" t="n">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H89" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I89" s="96" t="str">
+        <x:v>Static planning row for Match 084; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J89" s="96" t="str"/>
+      <x:c r="K89" s="99" t="str">
+        <x:f>IF(J89="","",IF(E89=J89,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" s="96" t="str">
+        <x:v>M085</x:v>
+      </x:c>
+      <x:c r="B90" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C90" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D90" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E90" s="96" t="str"/>
+      <x:c r="F90" s="96" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G90" s="99" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H90" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I90" s="96" t="str">
+        <x:v>Static planning row for Match 085; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J90" s="96" t="str"/>
+      <x:c r="K90" s="99" t="str">
+        <x:f>IF(J90="","",IF(E90=J90,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" s="96" t="str">
+        <x:v>M086</x:v>
+      </x:c>
+      <x:c r="B91" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C91" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D91" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E91" s="96" t="str"/>
+      <x:c r="F91" s="96" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G91" s="99" t="n">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="H91" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I91" s="96" t="str">
+        <x:v>Static planning row for Match 086; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J91" s="96" t="str"/>
+      <x:c r="K91" s="99" t="str">
+        <x:f>IF(J91="","",IF(E91=J91,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" s="96" t="str">
+        <x:v>M087</x:v>
+      </x:c>
+      <x:c r="B92" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C92" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D92" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E92" s="96" t="str"/>
+      <x:c r="F92" s="96" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G92" s="99" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="H92" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I92" s="96" t="str">
+        <x:v>Static planning row for Match 087; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J92" s="96" t="str"/>
+      <x:c r="K92" s="99" t="str">
+        <x:f>IF(J92="","",IF(E92=J92,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" s="96" t="str">
+        <x:v>M088</x:v>
+      </x:c>
+      <x:c r="B93" s="96" t="str">
+        <x:v>Round of 32</x:v>
+      </x:c>
+      <x:c r="C93" s="96" t="str">
+        <x:v>Round of 32 Side A</x:v>
+      </x:c>
+      <x:c r="D93" s="96" t="str">
+        <x:v>Round of 32 Side B</x:v>
+      </x:c>
+      <x:c r="E93" s="96" t="str"/>
+      <x:c r="F93" s="96" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G93" s="99" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="H93" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I93" s="96" t="str">
+        <x:v>Static planning row for Match 088; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J93" s="96" t="str"/>
+      <x:c r="K93" s="99" t="str">
+        <x:f>IF(J93="","",IF(E93=J93,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" s="96" t="str">
+        <x:v>M089</x:v>
+      </x:c>
+      <x:c r="B94" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C94" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D94" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E94" s="96" t="str"/>
+      <x:c r="F94" s="96" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G94" s="99" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H94" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I94" s="96" t="str">
+        <x:v>Static planning row for Match 089; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J94" s="96" t="str"/>
+      <x:c r="K94" s="99" t="str">
+        <x:f>IF(J94="","",IF(E94=J94,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" s="96" t="str">
+        <x:v>M090</x:v>
+      </x:c>
+      <x:c r="B95" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C95" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D95" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E95" s="96" t="str"/>
+      <x:c r="F95" s="96" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G95" s="99" t="n">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="H95" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I95" s="96" t="str">
+        <x:v>Static planning row for Match 090; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J95" s="96" t="str"/>
+      <x:c r="K95" s="99" t="str">
+        <x:f>IF(J95="","",IF(E95=J95,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" s="96" t="str">
+        <x:v>M091</x:v>
+      </x:c>
+      <x:c r="B96" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C96" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D96" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E96" s="96" t="str"/>
+      <x:c r="F96" s="96" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G96" s="99" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="H96" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I96" s="96" t="str">
+        <x:v>Static planning row for Match 091; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J96" s="96" t="str"/>
+      <x:c r="K96" s="99" t="str">
+        <x:f>IF(J96="","",IF(E96=J96,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" s="96" t="str">
+        <x:v>M092</x:v>
+      </x:c>
+      <x:c r="B97" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C97" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D97" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E97" s="96" t="str"/>
+      <x:c r="F97" s="96" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G97" s="99" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H97" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I97" s="96" t="str">
+        <x:v>Static planning row for Match 092; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J97" s="96" t="str"/>
+      <x:c r="K97" s="99" t="str">
+        <x:f>IF(J97="","",IF(E97=J97,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" s="96" t="str">
+        <x:v>M093</x:v>
+      </x:c>
+      <x:c r="B98" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C98" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D98" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E98" s="96" t="str"/>
+      <x:c r="F98" s="96" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G98" s="99" t="n">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H98" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I98" s="96" t="str">
+        <x:v>Static planning row for Match 093; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J98" s="96" t="str"/>
+      <x:c r="K98" s="99" t="str">
+        <x:f>IF(J98="","",IF(E98=J98,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="96" t="str">
+        <x:v>M094</x:v>
+      </x:c>
+      <x:c r="B99" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C99" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D99" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E99" s="96" t="str"/>
+      <x:c r="F99" s="96" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G99" s="99" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="H99" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I99" s="96" t="str">
+        <x:v>Static planning row for Match 094; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J99" s="96" t="str"/>
+      <x:c r="K99" s="99" t="str">
+        <x:f>IF(J99="","",IF(E99=J99,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="96" t="str">
+        <x:v>M095</x:v>
+      </x:c>
+      <x:c r="B100" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C100" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D100" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E100" s="96" t="str"/>
+      <x:c r="F100" s="96" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G100" s="99" t="n">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H100" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I100" s="96" t="str">
+        <x:v>Static planning row for Match 095; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J100" s="96" t="str"/>
+      <x:c r="K100" s="99" t="str">
+        <x:f>IF(J100="","",IF(E100=J100,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" s="96" t="str">
+        <x:v>M096</x:v>
+      </x:c>
+      <x:c r="B101" s="96" t="str">
+        <x:v>Round of 16</x:v>
+      </x:c>
+      <x:c r="C101" s="96" t="str">
+        <x:v>Round of 16 Side A</x:v>
+      </x:c>
+      <x:c r="D101" s="96" t="str">
+        <x:v>Round of 16 Side B</x:v>
+      </x:c>
+      <x:c r="E101" s="96" t="str"/>
+      <x:c r="F101" s="96" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G101" s="99" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H101" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I101" s="96" t="str">
+        <x:v>Static planning row for Match 096; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J101" s="96" t="str"/>
+      <x:c r="K101" s="99" t="str">
+        <x:f>IF(J101="","",IF(E101=J101,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" s="96" t="str">
+        <x:v>M097</x:v>
+      </x:c>
+      <x:c r="B102" s="96" t="str">
+        <x:v>Quarterfinal</x:v>
+      </x:c>
+      <x:c r="C102" s="96" t="str">
+        <x:v>Quarterfinal Side A</x:v>
+      </x:c>
+      <x:c r="D102" s="96" t="str">
+        <x:v>Quarterfinal Side B</x:v>
+      </x:c>
+      <x:c r="E102" s="96" t="str"/>
+      <x:c r="F102" s="96" t="str">
+        <x:v>Balanced</x:v>
+      </x:c>
+      <x:c r="G102" s="99" t="n">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H102" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I102" s="96" t="str">
+        <x:v>Static planning row for Match 097; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J102" s="96" t="str"/>
+      <x:c r="K102" s="99" t="str">
+        <x:f>IF(J102="","",IF(E102=J102,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" s="96" t="str">
+        <x:v>M098</x:v>
+      </x:c>
+      <x:c r="B103" s="96" t="str">
+        <x:v>Quarterfinal</x:v>
+      </x:c>
+      <x:c r="C103" s="96" t="str">
+        <x:v>Quarterfinal Side A</x:v>
+      </x:c>
+      <x:c r="D103" s="96" t="str">
+        <x:v>Quarterfinal Side B</x:v>
+      </x:c>
+      <x:c r="E103" s="96" t="str"/>
+      <x:c r="F103" s="96" t="str">
+        <x:v>Upset Watch</x:v>
+      </x:c>
+      <x:c r="G103" s="99" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="H103" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I103" s="96" t="str">
+        <x:v>Static planning row for Match 098; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J103" s="96" t="str"/>
+      <x:c r="K103" s="99" t="str">
+        <x:f>IF(J103="","",IF(E103=J103,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" s="96" t="str">
+        <x:v>M099</x:v>
+      </x:c>
+      <x:c r="B104" s="96" t="str">
+        <x:v>Quarterfinal</x:v>
+      </x:c>
+      <x:c r="C104" s="96" t="str">
+        <x:v>Quarterfinal Side A</x:v>
+      </x:c>
+      <x:c r="D104" s="96" t="str">
+        <x:v>Quarterfinal Side B</x:v>
+      </x:c>
+      <x:c r="E104" s="96" t="str"/>
+      <x:c r="F104" s="96" t="str">
+        <x:v>High Tempo</x:v>
+      </x:c>
+      <x:c r="G104" s="99" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H104" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I104" s="96" t="str">
+        <x:v>Static planning row for Match 099; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J104" s="96" t="str"/>
+      <x:c r="K104" s="99" t="str">
+        <x:f>IF(J104="","",IF(E104=J104,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" s="96" t="str">
+        <x:v>M100</x:v>
+      </x:c>
+      <x:c r="B105" s="96" t="str">
+        <x:v>Quarterfinal</x:v>
+      </x:c>
+      <x:c r="C105" s="96" t="str">
+        <x:v>Quarterfinal Side A</x:v>
+      </x:c>
+      <x:c r="D105" s="96" t="str">
+        <x:v>Quarterfinal Side B</x:v>
+      </x:c>
+      <x:c r="E105" s="96" t="str"/>
+      <x:c r="F105" s="96" t="str">
+        <x:v>Defense Edge</x:v>
+      </x:c>
+      <x:c r="G105" s="99" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H105" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I105" s="96" t="str">
+        <x:v>Static planning row for Match 100; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J105" s="96" t="str"/>
+      <x:c r="K105" s="99" t="str">
+        <x:f>IF(J105="","",IF(E105=J105,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" s="96" t="str">
+        <x:v>M101</x:v>
+      </x:c>
+      <x:c r="B106" s="96" t="str">
+        <x:v>Semifinal</x:v>
+      </x:c>
+      <x:c r="C106" s="96" t="str">
+        <x:v>Semifinal Side A</x:v>
+      </x:c>
+      <x:c r="D106" s="96" t="str">
+        <x:v>Semifinal Side B</x:v>
+      </x:c>
+      <x:c r="E106" s="96" t="str"/>
+      <x:c r="F106" s="96" t="str">
+        <x:v>Set-Piece Edge</x:v>
+      </x:c>
+      <x:c r="G106" s="99" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H106" s="96" t="str">
+        <x:v>Normal</x:v>
+      </x:c>
+      <x:c r="I106" s="96" t="str">
+        <x:v>Static planning row for Match 101; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J106" s="96" t="str"/>
+      <x:c r="K106" s="99" t="str">
+        <x:f>IF(J106="","",IF(E106=J106,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" s="96" t="str">
+        <x:v>M102</x:v>
+      </x:c>
+      <x:c r="B107" s="96" t="str">
+        <x:v>Semifinal</x:v>
+      </x:c>
+      <x:c r="C107" s="96" t="str">
+        <x:v>Semifinal Side A</x:v>
+      </x:c>
+      <x:c r="D107" s="96" t="str">
+        <x:v>Semifinal Side B</x:v>
+      </x:c>
+      <x:c r="E107" s="96" t="str"/>
+      <x:c r="F107" s="96" t="str">
+        <x:v>Momentum Swing</x:v>
+      </x:c>
+      <x:c r="G107" s="99" t="n">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H107" s="96" t="str">
+        <x:v>Watch</x:v>
+      </x:c>
+      <x:c r="I107" s="96" t="str">
+        <x:v>Static planning row for Match 102; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J107" s="96" t="str"/>
+      <x:c r="K107" s="99" t="str">
+        <x:f>IF(J107="","",IF(E107=J107,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" s="96" t="str">
+        <x:v>M103</x:v>
+      </x:c>
+      <x:c r="B108" s="96" t="str">
+        <x:v>Third Place</x:v>
+      </x:c>
+      <x:c r="C108" s="96" t="str">
+        <x:v>Third Place Side A</x:v>
+      </x:c>
+      <x:c r="D108" s="96" t="str">
+        <x:v>Third Place Side B</x:v>
+      </x:c>
+      <x:c r="E108" s="96" t="str"/>
+      <x:c r="F108" s="96" t="str">
+        <x:v>Low Block Risk</x:v>
+      </x:c>
+      <x:c r="G108" s="99" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H108" s="96" t="str">
+        <x:v>High</x:v>
+      </x:c>
+      <x:c r="I108" s="96" t="str">
+        <x:v>Static planning row for Match 103; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J108" s="96" t="str"/>
+      <x:c r="K108" s="99" t="str">
+        <x:f>IF(J108="","",IF(E108=J108,3,0))</x:f>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" s="96" t="str">
+        <x:v>M104</x:v>
+      </x:c>
+      <x:c r="B109" s="96" t="str">
+        <x:v>Final</x:v>
+      </x:c>
+      <x:c r="C109" s="96" t="str">
+        <x:v>Final Side A</x:v>
+      </x:c>
+      <x:c r="D109" s="96" t="str">
+        <x:v>Final Side B</x:v>
+      </x:c>
+      <x:c r="E109" s="96" t="str"/>
+      <x:c r="F109" s="96" t="str">
+        <x:v>Pressing Edge</x:v>
+      </x:c>
+      <x:c r="G109" s="99" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H109" s="96" t="str">
+        <x:v>Must Watch</x:v>
+      </x:c>
+      <x:c r="I109" s="96" t="str">
+        <x:v>Static planning row for Match 104; edit teams, prediction, result, and notes during demo.</x:v>
+      </x:c>
+      <x:c r="J109" s="96" t="str"/>
+      <x:c r="K109" s="99" t="str">
+        <x:f>IF(J109="","",IF(E109=J109,3,0))</x:f>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:K1"/>
+    <x:mergeCell ref="A2:K2"/>
+  </x:mergeCells>
+  <x:conditionalFormatting sqref="G6:G109">
+    <x:cfRule type="dataBar" priority="1">
+      <x:dataBar>
+        <x:cfvo type="min"/>
+        <x:cfvo type="max"/>
+        <x:color rgb="FF10B981"/>
+      </x:dataBar>
+      <x:extLst>
+        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{0CE2D498-E226-FF2D-5C23-B52D5D565896}</x14:id>
+        </x:ext>
+      </x:extLst>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:conditionalFormatting sqref="K6:K109">
+    <x:cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <x:formula>0</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="2">
+    <x:dataValidation type="list" sqref="H6:H109">
+      <x:formula1>"Normal,Watch,High,Must Watch"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="F6:F109">
+      <x:formula1>"Balanced,Upset Watch,High Tempo,Defense Edge,Set-Piece Edge,Momentum Swing,Low Block Risk,Pressing Edge"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R48521e9690004e89"/>
+  </x:tableParts>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting>
+          <x14:cfRule type="dataBar" priority="1" id="{0CE2D498-E226-FF2D-5C23-B52D5D565896}">
+            <x14:dataBar gradient="1">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:fillColor rgb="FF10B981"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G6:G109</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </x:ext>
+  </x:extLst>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="14" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="14" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="71" t="str">
+        <x:v>FRIENDS LEAGUE — HACKATHON SCORING BOARD</x:v>
+      </x:c>
+      <x:c r="B1" s="74"/>
+      <x:c r="C1" s="74"/>
+      <x:c r="D1" s="74"/>
+      <x:c r="E1" s="74"/>
+      <x:c r="F1" s="74"/>
+      <x:c r="G1" s="74"/>
+      <x:c r="H1" s="4"/>
+      <x:c r="I1" s="4"/>
+      <x:c r="J1" s="4"/>
+      <x:c r="K1" s="4"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="17" t="str">
+        <x:v>Private league board for AI vs Me / friends challenge. Static editable inputs with formula-driven Total Points.</x:v>
+      </x:c>
+      <x:c r="B2" s="4"/>
+      <x:c r="C2" s="4"/>
+      <x:c r="D2" s="4"/>
+      <x:c r="E2" s="4"/>
+      <x:c r="F2" s="4"/>
+      <x:c r="G2" s="4"/>
+      <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
+      <x:c r="J2" s="4"/>
+      <x:c r="K2" s="4"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="4" t="str">
+        <x:v>Navigation</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="e">
+        <x:f>HYPERLINK("#'START_HERE'!A1","Back to START")</x:f>
+      </x:c>
+      <x:c r="C3" s="4" t="e">
+        <x:f>HYPERLINK("#'MATCH_PLANNER'!A1","Match Planner")</x:f>
+      </x:c>
+      <x:c r="D3" s="4"/>
+      <x:c r="E3" s="4"/>
+      <x:c r="F3" s="4"/>
+      <x:c r="G3" s="4"/>
+      <x:c r="H3" s="4"/>
+      <x:c r="I3" s="4"/>
+      <x:c r="J3" s="4"/>
+      <x:c r="K3" s="4"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="4"/>
+      <x:c r="B4" s="4"/>
+      <x:c r="C4" s="4"/>
+      <x:c r="D4" s="4"/>
+      <x:c r="E4" s="4"/>
+      <x:c r="F4" s="4"/>
+      <x:c r="G4" s="4"/>
+      <x:c r="H4" s="4"/>
+      <x:c r="I4" s="4"/>
+      <x:c r="J4" s="4"/>
+      <x:c r="K4" s="4"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="79" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="B5" s="79" t="str">
+        <x:v>Role</x:v>
+      </x:c>
+      <x:c r="C5" s="79" t="str">
+        <x:v>Correct Scores</x:v>
+      </x:c>
+      <x:c r="D5" s="79" t="str">
+        <x:v>Correct Winners</x:v>
+      </x:c>
+      <x:c r="E5" s="79" t="str">
+        <x:v>Upsets Hit</x:v>
+      </x:c>
+      <x:c r="F5" s="79" t="str">
+        <x:v>Total Points</x:v>
+      </x:c>
+      <x:c r="G5" s="79" t="str">
         <x:v>Status</x:v>
       </x:c>
-      <x:c r="C5" s="26" t="str">
-        <x:v>Implementation</x:v>
-      </x:c>
-      <x:c r="D5" s="4"/>
-      <x:c r="E5" s="4"/>
-      <x:c r="F5" s="4"/>
-      <x:c r="G5" s="4"/>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
       <x:c r="K5" s="4"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>Product Mode</x:v>
-      </x:c>
-      <x:c r="B6" s="33" t="str">
-        <x:v>Unofficial fan-made football tournament planner</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="str">
-        <x:v>Digital download / spreadsheet-first planning asset</x:v>
-      </x:c>
-      <x:c r="D6" s="4"/>
-      <x:c r="E6" s="4"/>
-      <x:c r="F6" s="4"/>
-      <x:c r="G6" s="4"/>
+      <x:c r="A6" s="84" t="str">
+        <x:v>Me</x:v>
+      </x:c>
+      <x:c r="B6" s="84" t="str">
+        <x:v>Owner</x:v>
+      </x:c>
+      <x:c r="C6" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D6" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="97" t="n">
+        <x:f>IF(A6="","",C6*3+D6*1+E6*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="84" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="4"/>
       <x:c r="J6" s="4"/>
       <x:c r="K6" s="4"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>Critical Fix</x:v>
-      </x:c>
-      <x:c r="B7" s="33" t="str">
-        <x:v>AnnexC_495 is embedded as 495 ordinary cell values</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="str">
-        <x:v>No live import functions or hidden web fetches</x:v>
-      </x:c>
-      <x:c r="D7" s="4"/>
-      <x:c r="E7" s="4"/>
-      <x:c r="F7" s="4"/>
-      <x:c r="G7" s="4"/>
+      <x:c r="A7" s="84" t="str">
+        <x:v>AI Scout</x:v>
+      </x:c>
+      <x:c r="B7" s="84" t="str">
+        <x:v>Benchmark</x:v>
+      </x:c>
+      <x:c r="C7" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D7" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="97" t="n">
+        <x:f>IF(A7="","",C7*3+D7*1+E7*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="84" t="str">
+        <x:v>Ready</x:v>
+      </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>Buyer UX</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>Use visible tabs only</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>START_HERE, BRACKET_WAR_ROOM, MATCH_PLANNER, FRIENDS_LEAGUE</x:v>
-      </x:c>
-      <x:c r="D8" s="4"/>
-      <x:c r="E8" s="4"/>
-      <x:c r="F8" s="4"/>
-      <x:c r="G8" s="4"/>
+      <x:c r="A8" s="84" t="str">
+        <x:v>Friend 01</x:v>
+      </x:c>
+      <x:c r="B8" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C8" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D8" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="97" t="n">
+        <x:f>IF(A8="","",C8*3+D8*1+E8*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="84" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>Developer Layer</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>AnnexC_495_STATIC + QA_STATIC_CHECK</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>Marked veryHidden inside XLSX package after export</x:v>
-      </x:c>
-      <x:c r="D9" s="4"/>
-      <x:c r="E9" s="4"/>
-      <x:c r="F9" s="4"/>
-      <x:c r="G9" s="4"/>
+      <x:c r="A9" s="84" t="str">
+        <x:v>Friend 02</x:v>
+      </x:c>
+      <x:c r="B9" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C9" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D9" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="97" t="n">
+        <x:f>IF(A9="","",C9*3+D9*1+E9*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="84" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>IP Boundary</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>Generic football tournament language only</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>No FIFA logo, emblem, mascot, crests, players, sponsors, or affiliation claim</x:v>
-      </x:c>
-      <x:c r="D10" s="4"/>
-      <x:c r="E10" s="4"/>
-      <x:c r="F10" s="4"/>
-      <x:c r="G10" s="4"/>
+      <x:c r="A10" s="84" t="str">
+        <x:v>Friend 03</x:v>
+      </x:c>
+      <x:c r="B10" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C10" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D10" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="97" t="n">
+        <x:f>IF(A10="","",C10*3+D10*1+E10*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G10" s="84" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>GoodNotes Upsell</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>Pair with PDF planner + sticker ZIP</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>Core workbook can be Tier 2/3 bundle proof asset</x:v>
-      </x:c>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
+      <x:c r="A11" s="84" t="str">
+        <x:v>Friend 04</x:v>
+      </x:c>
+      <x:c r="B11" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C11" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D11" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E11" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="97" t="n">
+        <x:f>IF(A11="","",C11*3+D11*1+E11*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="84" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H11" s="4"/>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
       <x:c r="K11" s="4"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="4"/>
-      <x:c r="B12" s="4"/>
-      <x:c r="C12" s="4"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
+      <x:c r="A12" s="84" t="str">
+        <x:v>Friend 05</x:v>
+      </x:c>
+      <x:c r="B12" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C12" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D12" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E12" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F12" s="97" t="n">
+        <x:f>IF(A12="","",C12*3+D12*1+E12*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G12" s="84" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H12" s="4"/>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
       <x:c r="K12" s="4"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="4"/>
-      <x:c r="B13" s="4"/>
-      <x:c r="C13" s="4"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
+      <x:c r="A13" s="84" t="str">
+        <x:v>Friend 06</x:v>
+      </x:c>
+      <x:c r="B13" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C13" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D13" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F13" s="97" t="n">
+        <x:f>IF(A13="","",C13*3+D13*1+E13*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G13" s="84" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
       <x:c r="K13" s="4"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
+      <x:c r="A14" s="90" t="str">
+        <x:v>Friend 07</x:v>
+      </x:c>
+      <x:c r="B14" s="90" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C14" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D14" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E14" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F14" s="98" t="n">
+        <x:f>IF(A14="","",C14*3+D14*1+E14*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G14" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H14" s="4"/>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
       <x:c r="K14" s="4"/>
     </x:row>
-    <x:row r="15" ht="22" customHeight="1">
-      <x:c r="A15" s="40" t="str">
-        <x:v>Risk</x:v>
-      </x:c>
-      <x:c r="B15" s="40" t="str">
-        <x:v>FIX6C Status</x:v>
-      </x:c>
-      <x:c r="C15" s="40" t="str">
-        <x:v>Reason</x:v>
-      </x:c>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
+    <x:row r="15">
+      <x:c r="A15" s="90" t="str">
+        <x:v>Friend 08</x:v>
+      </x:c>
+      <x:c r="B15" s="90" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C15" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D15" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E15" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F15" s="98" t="n">
+        <x:f>IF(A15="","",C15*3+D15*1+E15*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G15" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H15" s="4"/>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
       <x:c r="K15" s="4"/>
     </x:row>
     <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>IMPORTHTML</x:v>
-      </x:c>
-      <x:c r="B16" s="33" t="str">
-        <x:v>REMOVED</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="str">
-        <x:v>No formulas contain IMPORTHTML/IMPORTXML/IMPORTDATA/IMPORTRANGE</x:v>
-      </x:c>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
+      <x:c r="A16" s="90" t="str">
+        <x:v>Friend 09</x:v>
+      </x:c>
+      <x:c r="B16" s="90" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C16" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D16" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E16" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F16" s="98" t="n">
+        <x:f>IF(A16="","",C16*3+D16*1+E16*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G16" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H16" s="4"/>
       <x:c r="I16" s="4"/>
       <x:c r="J16" s="4"/>
       <x:c r="K16" s="4"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>#NAME?</x:v>
-      </x:c>
-      <x:c r="B17" s="33" t="str">
-        <x:v>BLOCKED BY DESIGN</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="str">
-        <x:v>No Google Sheets-only custom functions or named function dependency</x:v>
-      </x:c>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
+      <x:c r="A17" s="90" t="str">
+        <x:v>Friend 10</x:v>
+      </x:c>
+      <x:c r="B17" s="90" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C17" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D17" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E17" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="98" t="n">
+        <x:f>IF(A17="","",C17*3+D17*1+E17*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G17" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H17" s="4"/>
       <x:c r="I17" s="4"/>
       <x:c r="J17" s="4"/>
       <x:c r="K17" s="4"/>
     </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>Array spill</x:v>
-      </x:c>
-      <x:c r="B18" s="33" t="str">
-        <x:v>REMOVED</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="str">
-        <x:v>No ARRAYFORMULA, FILTER, QUERY, SORT, UNIQUE, TRANSPOSE or spill dependency</x:v>
-      </x:c>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="92" t="str">
+        <x:v>Friend 11</x:v>
+      </x:c>
+      <x:c r="B18" s="92" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C18" s="100" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D18" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F18" s="98" t="n">
+        <x:f>IF(A18="","",C18*3+D18*1+E18*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G18" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H18" s="4"/>
       <x:c r="I18" s="4"/>
       <x:c r="J18" s="4"/>
       <x:c r="K18" s="4"/>
     </x:row>
     <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>Paste special</x:v>
-      </x:c>
-      <x:c r="B19" s="33" t="str">
-        <x:v>NOT REQUIRED</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="str">
-        <x:v>AnnexC data is stored directly as ordinary workbook values</x:v>
-      </x:c>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
+      <x:c r="A19" s="84" t="str">
+        <x:v>Friend 12</x:v>
+      </x:c>
+      <x:c r="B19" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C19" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D19" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="98" t="n">
+        <x:f>IF(A19="","",C19*3+D19*1+E19*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H19" s="4"/>
       <x:c r="I19" s="4"/>
       <x:c r="J19" s="4"/>
       <x:c r="K19" s="4"/>
     </x:row>
     <x:row r="20">
-      <x:c r="A20" s="33" t="str">
-        <x:v>Buyer dev-layer exposure</x:v>
-      </x:c>
-      <x:c r="B20" s="33" t="str">
-        <x:v>HIDDEN</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="str">
-        <x:v>Internal sheets are set to veryHidden in workbook XML</x:v>
-      </x:c>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
+      <x:c r="A20" s="84" t="str">
+        <x:v>Friend 13</x:v>
+      </x:c>
+      <x:c r="B20" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C20" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D20" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="98" t="n">
+        <x:f>IF(A20="","",C20*3+D20*1+E20*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H20" s="4"/>
       <x:c r="I20" s="4"/>
       <x:c r="J20" s="4"/>
       <x:c r="K20" s="4"/>
     </x:row>
     <x:row r="21">
-      <x:c r="A21" s="4"/>
-      <x:c r="B21" s="4"/>
-      <x:c r="C21" s="4"/>
-      <x:c r="D21" s="4"/>
-      <x:c r="E21" s="4"/>
-      <x:c r="F21" s="4"/>
-      <x:c r="G21" s="4"/>
+      <x:c r="A21" s="84" t="str">
+        <x:v>Friend 14</x:v>
+      </x:c>
+      <x:c r="B21" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C21" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D21" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="98" t="n">
+        <x:f>IF(A21="","",C21*3+D21*1+E21*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H21" s="4"/>
       <x:c r="I21" s="4"/>
       <x:c r="J21" s="4"/>
       <x:c r="K21" s="4"/>
     </x:row>
     <x:row r="22">
-      <x:c r="A22" s="4"/>
-      <x:c r="B22" s="4"/>
-      <x:c r="C22" s="4"/>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
+      <x:c r="A22" s="84" t="str">
+        <x:v>Friend 15</x:v>
+      </x:c>
+      <x:c r="B22" s="84" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C22" s="97" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D22" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E22" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F22" s="98" t="n">
+        <x:f>IF(A22="","",C22*3+D22*1+E22*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G22" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H22" s="4"/>
       <x:c r="I22" s="4"/>
       <x:c r="J22" s="4"/>
       <x:c r="K22" s="4"/>
     </x:row>
     <x:row r="23">
-      <x:c r="A23" s="4"/>
-      <x:c r="B23" s="4"/>
-      <x:c r="C23" s="4"/>
-      <x:c r="D23" s="4"/>
-      <x:c r="E23" s="4"/>
-      <x:c r="F23" s="4"/>
-      <x:c r="G23" s="4"/>
+      <x:c r="A23" s="90" t="str">
+        <x:v>Friend 16</x:v>
+      </x:c>
+      <x:c r="B23" s="90" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C23" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D23" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E23" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F23" s="98" t="n">
+        <x:f>IF(A23="","",C23*3+D23*1+E23*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G23" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H23" s="4"/>
       <x:c r="I23" s="4"/>
       <x:c r="J23" s="4"/>
       <x:c r="K23" s="4"/>
     </x:row>
-    <x:row r="24" ht="22" customHeight="1">
-      <x:c r="A24" s="50" t="str">
-        <x:v>Tier</x:v>
-      </x:c>
-      <x:c r="B24" s="50" t="str">
-        <x:v>Price</x:v>
-      </x:c>
-      <x:c r="C24" s="50" t="str">
-        <x:v>Bundle</x:v>
-      </x:c>
-      <x:c r="D24" s="50" t="str">
-        <x:v>Upsell Hook</x:v>
-      </x:c>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
+    <x:row r="24">
+      <x:c r="A24" s="90" t="str">
+        <x:v>Friend 17</x:v>
+      </x:c>
+      <x:c r="B24" s="90" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C24" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D24" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E24" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F24" s="98" t="n">
+        <x:f>IF(A24="","",C24*3+D24*1+E24*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G24" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H24" s="4"/>
       <x:c r="I24" s="4"/>
       <x:c r="J24" s="4"/>
       <x:c r="K24" s="4"/>
     </x:row>
     <x:row r="25">
-      <x:c r="A25" s="33" t="str">
-        <x:v>Tier 1</x:v>
-      </x:c>
-      <x:c r="B25" s="33" t="str">
-        <x:v>$12–15</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="str">
-        <x:v>Core hyperlinked PDF + static workbook bonus</x:v>
-      </x:c>
-      <x:c r="D25" s="33" t="str">
-        <x:v>Use workbook as anti-friction proof</x:v>
-      </x:c>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
+      <x:c r="A25" s="90" t="str">
+        <x:v>Friend 18</x:v>
+      </x:c>
+      <x:c r="B25" s="90" t="str">
+        <x:v>Player</x:v>
+      </x:c>
+      <x:c r="C25" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D25" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E25" s="98" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F25" s="98" t="n">
+        <x:f>IF(A25="","",C25*3+D25*1+E25*2)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G25" s="90" t="str">
+        <x:v>Invite sent</x:v>
+      </x:c>
       <x:c r="H25" s="4"/>
       <x:c r="I25" s="4"/>
       <x:c r="J25" s="4"/>
       <x:c r="K25" s="4"/>
     </x:row>
     <x:row r="26">
-      <x:c r="A26" s="33" t="str">
-        <x:v>Tier 2</x:v>
-      </x:c>
-      <x:c r="B26" s="33" t="str">
-        <x:v>$18–22</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="str">
-        <x:v>PDF + stickers + printable + workbook</x:v>
-      </x:c>
-      <x:c r="D26" s="33" t="str">
-        <x:v>Best Etsy value-stack tier</x:v>
-      </x:c>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
+      <x:c r="A26" s="90"/>
+      <x:c r="B26" s="90"/>
+      <x:c r="C26" s="90"/>
+      <x:c r="D26" s="90"/>
+      <x:c r="E26" s="90"/>
+      <x:c r="F26" s="90"/>
+      <x:c r="G26" s="90"/>
       <x:c r="H26" s="4"/>
       <x:c r="I26" s="4"/>
       <x:c r="J26" s="4"/>
       <x:c r="K26" s="4"/>
     </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="33" t="str">
-        <x:v>Tier 3</x:v>
-      </x:c>
-      <x:c r="B27" s="33" t="str">
-        <x:v>$25–30</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="str">
-        <x:v>Ultimate command center bundle</x:v>
-      </x:c>
-      <x:c r="D27" s="33" t="str">
-        <x:v>Add AI Tactical Slip workflow, league board, compatibility guide</x:v>
-      </x:c>
-      <x:c r="E27" s="4"/>
-      <x:c r="F27" s="4"/>
-      <x:c r="G27" s="4"/>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="82" t="str">
+        <x:v>Rule</x:v>
+      </x:c>
+      <x:c r="B27" s="82" t="str">
+        <x:v>Points</x:v>
+      </x:c>
+      <x:c r="C27" s="82" t="str">
+        <x:v>Definition</x:v>
+      </x:c>
+      <x:c r="D27" s="90"/>
+      <x:c r="E27" s="90"/>
+      <x:c r="F27" s="90"/>
+      <x:c r="G27" s="90"/>
       <x:c r="H27" s="4"/>
       <x:c r="I27" s="4"/>
       <x:c r="J27" s="4"/>
       <x:c r="K27" s="4"/>
     </x:row>
     <x:row r="28">
-      <x:c r="A28" s="4"/>
-      <x:c r="B28" s="4"/>
-      <x:c r="C28" s="4"/>
-      <x:c r="D28" s="4"/>
-      <x:c r="E28" s="4"/>
-      <x:c r="F28" s="4"/>
-      <x:c r="G28" s="4"/>
+      <x:c r="A28" s="90" t="str">
+        <x:v>Correct score</x:v>
+      </x:c>
+      <x:c r="B28" s="90" t="str">
+        <x:v>3 pts</x:v>
+      </x:c>
+      <x:c r="C28" s="90" t="str">
+        <x:v>Exact result prediction</x:v>
+      </x:c>
+      <x:c r="D28" s="90"/>
+      <x:c r="E28" s="90"/>
+      <x:c r="F28" s="90"/>
+      <x:c r="G28" s="90"/>
       <x:c r="H28" s="4"/>
       <x:c r="I28" s="4"/>
       <x:c r="J28" s="4"/>
       <x:c r="K28" s="4"/>
     </x:row>
     <x:row r="29">
-      <x:c r="A29" s="4"/>
-      <x:c r="B29" s="4"/>
-      <x:c r="C29" s="4"/>
-      <x:c r="D29" s="4"/>
-      <x:c r="E29" s="4"/>
-      <x:c r="F29" s="4"/>
-      <x:c r="G29" s="4"/>
+      <x:c r="A29" s="90" t="str">
+        <x:v>Correct winner</x:v>
+      </x:c>
+      <x:c r="B29" s="90" t="str">
+        <x:v>1 pt</x:v>
+      </x:c>
+      <x:c r="C29" s="90" t="str">
+        <x:v>Winner/draw direction correct</x:v>
+      </x:c>
+      <x:c r="D29" s="90"/>
+      <x:c r="E29" s="90"/>
+      <x:c r="F29" s="90"/>
+      <x:c r="G29" s="90"/>
       <x:c r="H29" s="4"/>
       <x:c r="I29" s="4"/>
       <x:c r="J29" s="4"/>
       <x:c r="K29" s="4"/>
     </x:row>
     <x:row r="30">
-      <x:c r="A30" s="4"/>
-      <x:c r="B30" s="4"/>
-      <x:c r="C30" s="4"/>
-      <x:c r="D30" s="4"/>
-      <x:c r="E30" s="4"/>
-      <x:c r="F30" s="4"/>
-      <x:c r="G30" s="4"/>
+      <x:c r="A30" s="90" t="str">
+        <x:v>Upset bonus</x:v>
+      </x:c>
+      <x:c r="B30" s="90" t="str">
+        <x:v>2 pts</x:v>
+      </x:c>
+      <x:c r="C30" s="90" t="str">
+        <x:v>Underdog marker lands</x:v>
+      </x:c>
+      <x:c r="D30" s="90"/>
+      <x:c r="E30" s="90"/>
+      <x:c r="F30" s="90"/>
+      <x:c r="G30" s="90"/>
       <x:c r="H30" s="4"/>
       <x:c r="I30" s="4"/>
       <x:c r="J30" s="4"/>
       <x:c r="K30" s="4"/>
     </x:row>
     <x:row r="31">
-      <x:c r="A31" s="4"/>
-      <x:c r="B31" s="4"/>
-      <x:c r="C31" s="4"/>
-      <x:c r="D31" s="4"/>
-      <x:c r="E31" s="4"/>
-      <x:c r="F31" s="4"/>
-      <x:c r="G31" s="4"/>
+      <x:c r="A31" s="90" t="str">
+        <x:v>Final champion</x:v>
+      </x:c>
+      <x:c r="B31" s="90" t="str">
+        <x:v>5 pts</x:v>
+      </x:c>
+      <x:c r="C31" s="90" t="str">
+        <x:v>Champion lock correct outside basic row formula</x:v>
+      </x:c>
+      <x:c r="D31" s="90"/>
+      <x:c r="E31" s="90"/>
+      <x:c r="F31" s="90"/>
+      <x:c r="G31" s="90"/>
       <x:c r="H31" s="4"/>
       <x:c r="I31" s="4"/>
       <x:c r="J31" s="4"/>
@@ -1126,695 +6406,6 @@
       <x:c r="J36" s="4"/>
       <x:c r="K36" s="4"/>
     </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:K1"/>
-    <x:mergeCell ref="A2:K2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="3">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf427a81f8e94251"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re059c518222f43ee"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R46214ac2adc04fe2"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="9" t="str">
-        <x:v>BRACKET WAR ROOM</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="4"/>
-      <x:c r="K1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="17" t="str">
-        <x:v>Static-value control board. Fill scores, notes, confidence, and upset signals without web formulas.</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
-      <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
-      <x:c r="H2" s="4"/>
-      <x:c r="I2" s="4"/>
-      <x:c r="J2" s="4"/>
-      <x:c r="K2" s="4"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="4"/>
-      <x:c r="B3" s="4"/>
-      <x:c r="C3" s="4"/>
-      <x:c r="D3" s="4"/>
-      <x:c r="E3" s="4"/>
-      <x:c r="F3" s="4"/>
-      <x:c r="G3" s="4"/>
-      <x:c r="H3" s="4"/>
-      <x:c r="I3" s="4"/>
-      <x:c r="J3" s="4"/>
-      <x:c r="K3" s="4"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="4"/>
-      <x:c r="B4" s="4"/>
-      <x:c r="C4" s="4"/>
-      <x:c r="D4" s="4"/>
-      <x:c r="E4" s="4"/>
-      <x:c r="F4" s="4"/>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
-      <x:c r="K4" s="4"/>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="26" t="str">
-        <x:v>Stage</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
-        <x:v>Slots</x:v>
-      </x:c>
-      <x:c r="C5" s="26" t="str">
-        <x:v>Tracking</x:v>
-      </x:c>
-      <x:c r="D5" s="26" t="str">
-        <x:v>Decision Rule</x:v>
-      </x:c>
-      <x:c r="E5" s="26" t="str">
-        <x:v>Input Mode</x:v>
-      </x:c>
-      <x:c r="F5" s="4"/>
-      <x:c r="G5" s="4"/>
-      <x:c r="H5" s="4"/>
-      <x:c r="I5" s="4"/>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>Group A</x:v>
-      </x:c>
-      <x:c r="B6" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D6" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E6" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F6" s="4"/>
-      <x:c r="G6" s="4"/>
-      <x:c r="H6" s="4"/>
-      <x:c r="I6" s="4"/>
-      <x:c r="J6" s="4"/>
-      <x:c r="K6" s="4"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>Group B</x:v>
-      </x:c>
-      <x:c r="B7" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D7" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E7" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F7" s="4"/>
-      <x:c r="G7" s="4"/>
-      <x:c r="H7" s="4"/>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
-      <x:c r="K7" s="4"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>Group C</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F8" s="4"/>
-      <x:c r="G8" s="4"/>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>Group D</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F9" s="4"/>
-      <x:c r="G9" s="4"/>
-      <x:c r="H9" s="4"/>
-      <x:c r="I9" s="4"/>
-      <x:c r="J9" s="4"/>
-      <x:c r="K9" s="4"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>Group E</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F10" s="4"/>
-      <x:c r="G10" s="4"/>
-      <x:c r="H10" s="4"/>
-      <x:c r="I10" s="4"/>
-      <x:c r="J10" s="4"/>
-      <x:c r="K10" s="4"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>Group F</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F11" s="4"/>
-      <x:c r="G11" s="4"/>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>Group G</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F12" s="4"/>
-      <x:c r="G12" s="4"/>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>Group H</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F13" s="4"/>
-      <x:c r="G13" s="4"/>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>Group I</x:v>
-      </x:c>
-      <x:c r="B14" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D14" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E14" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>Group J</x:v>
-      </x:c>
-      <x:c r="B15" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D15" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E15" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>Group K</x:v>
-      </x:c>
-      <x:c r="B16" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D16" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E16" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>Group L</x:v>
-      </x:c>
-      <x:c r="B17" s="33" t="str">
-        <x:v>4 teams</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="str">
-        <x:v>Track W-D-L, GD, PTS</x:v>
-      </x:c>
-      <x:c r="D17" s="33" t="str">
-        <x:v>Top 2 + selected 3rd-place logic</x:v>
-      </x:c>
-      <x:c r="E17" s="33" t="str">
-        <x:v>Manual buyer input</x:v>
-      </x:c>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="4"/>
-      <x:c r="B18" s="4"/>
-      <x:c r="C18" s="4"/>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="4"/>
-      <x:c r="B19" s="4"/>
-      <x:c r="C19" s="4"/>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
-      <x:c r="H19" s="4"/>
-      <x:c r="I19" s="4"/>
-      <x:c r="J19" s="4"/>
-      <x:c r="K19" s="4"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="4"/>
-      <x:c r="B20" s="4"/>
-      <x:c r="C20" s="4"/>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
-      <x:c r="H20" s="4"/>
-      <x:c r="I20" s="4"/>
-      <x:c r="J20" s="4"/>
-      <x:c r="K20" s="4"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="4"/>
-      <x:c r="B21" s="4"/>
-      <x:c r="C21" s="4"/>
-      <x:c r="D21" s="4"/>
-      <x:c r="E21" s="4"/>
-      <x:c r="F21" s="4"/>
-      <x:c r="G21" s="4"/>
-      <x:c r="H21" s="4"/>
-      <x:c r="I21" s="4"/>
-      <x:c r="J21" s="4"/>
-      <x:c r="K21" s="4"/>
-    </x:row>
-    <x:row r="22" ht="22" customHeight="1">
-      <x:c r="A22" s="60" t="str">
-        <x:v>Knockout Stage</x:v>
-      </x:c>
-      <x:c r="B22" s="60" t="str">
-        <x:v>Match Count</x:v>
-      </x:c>
-      <x:c r="C22" s="60" t="str">
-        <x:v>Output</x:v>
-      </x:c>
-      <x:c r="D22" s="60" t="str">
-        <x:v>Planning Hook</x:v>
-      </x:c>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="33" t="str">
-        <x:v>Round of 32</x:v>
-      </x:c>
-      <x:c r="B23" s="33" t="str">
-        <x:v>16 matches</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="str">
-        <x:v>Winner advances</x:v>
-      </x:c>
-      <x:c r="D23" s="33" t="str">
-        <x:v>Upset marker + confidence note</x:v>
-      </x:c>
-      <x:c r="E23" s="4"/>
-      <x:c r="F23" s="4"/>
-      <x:c r="G23" s="4"/>
-      <x:c r="H23" s="4"/>
-      <x:c r="I23" s="4"/>
-      <x:c r="J23" s="4"/>
-      <x:c r="K23" s="4"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="33" t="str">
-        <x:v>Round of 16</x:v>
-      </x:c>
-      <x:c r="B24" s="33" t="str">
-        <x:v>8 matches</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="str">
-        <x:v>Winner advances</x:v>
-      </x:c>
-      <x:c r="D24" s="33" t="str">
-        <x:v>Tactical slip comparison</x:v>
-      </x:c>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="33" t="str">
-        <x:v>Quarterfinal</x:v>
-      </x:c>
-      <x:c r="B25" s="33" t="str">
-        <x:v>4 matches</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="str">
-        <x:v>Winner advances</x:v>
-      </x:c>
-      <x:c r="D25" s="33" t="str">
-        <x:v>High-stakes watchlist</x:v>
-      </x:c>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="33" t="str">
-        <x:v>Semifinal</x:v>
-      </x:c>
-      <x:c r="B26" s="33" t="str">
-        <x:v>2 matches</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="str">
-        <x:v>Winner advances</x:v>
-      </x:c>
-      <x:c r="D26" s="33" t="str">
-        <x:v>Finalist prediction lock</x:v>
-      </x:c>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
-      <x:c r="H26" s="4"/>
-      <x:c r="I26" s="4"/>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="33" t="str">
-        <x:v>Third Place</x:v>
-      </x:c>
-      <x:c r="B27" s="33" t="str">
-        <x:v>1 match</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="str">
-        <x:v>Optional tracking</x:v>
-      </x:c>
-      <x:c r="D27" s="33" t="str">
-        <x:v>Printable party note</x:v>
-      </x:c>
-      <x:c r="E27" s="4"/>
-      <x:c r="F27" s="4"/>
-      <x:c r="G27" s="4"/>
-      <x:c r="H27" s="4"/>
-      <x:c r="I27" s="4"/>
-      <x:c r="J27" s="4"/>
-      <x:c r="K27" s="4"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="33" t="str">
-        <x:v>Final</x:v>
-      </x:c>
-      <x:c r="B28" s="33" t="str">
-        <x:v>1 match</x:v>
-      </x:c>
-      <x:c r="C28" s="33" t="str">
-        <x:v>Champion</x:v>
-      </x:c>
-      <x:c r="D28" s="33" t="str">
-        <x:v>Winner/champion generic football cup marker</x:v>
-      </x:c>
-      <x:c r="E28" s="4"/>
-      <x:c r="F28" s="4"/>
-      <x:c r="G28" s="4"/>
-      <x:c r="H28" s="4"/>
-      <x:c r="I28" s="4"/>
-      <x:c r="J28" s="4"/>
-      <x:c r="K28" s="4"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="4"/>
-      <x:c r="B29" s="4"/>
-      <x:c r="C29" s="4"/>
-      <x:c r="D29" s="4"/>
-      <x:c r="E29" s="4"/>
-      <x:c r="F29" s="4"/>
-      <x:c r="G29" s="4"/>
-      <x:c r="H29" s="4"/>
-      <x:c r="I29" s="4"/>
-      <x:c r="J29" s="4"/>
-      <x:c r="K29" s="4"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="4"/>
-      <x:c r="B30" s="4"/>
-      <x:c r="C30" s="4"/>
-      <x:c r="D30" s="4"/>
-      <x:c r="E30" s="4"/>
-      <x:c r="F30" s="4"/>
-      <x:c r="G30" s="4"/>
-      <x:c r="H30" s="4"/>
-      <x:c r="I30" s="4"/>
-      <x:c r="J30" s="4"/>
-      <x:c r="K30" s="4"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="4"/>
-      <x:c r="B31" s="4"/>
-      <x:c r="C31" s="4"/>
-      <x:c r="D31" s="4"/>
-      <x:c r="E31" s="4"/>
-      <x:c r="F31" s="4"/>
-      <x:c r="G31" s="4"/>
-      <x:c r="H31" s="4"/>
-      <x:c r="I31" s="4"/>
-      <x:c r="J31" s="4"/>
-      <x:c r="K31" s="4"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="4"/>
-      <x:c r="B32" s="4"/>
-      <x:c r="C32" s="4"/>
-      <x:c r="D32" s="4"/>
-      <x:c r="E32" s="4"/>
-      <x:c r="F32" s="4"/>
-      <x:c r="G32" s="4"/>
-      <x:c r="H32" s="4"/>
-      <x:c r="I32" s="4"/>
-      <x:c r="J32" s="4"/>
-      <x:c r="K32" s="4"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="4"/>
-      <x:c r="B33" s="4"/>
-      <x:c r="C33" s="4"/>
-      <x:c r="D33" s="4"/>
-      <x:c r="E33" s="4"/>
-      <x:c r="F33" s="4"/>
-      <x:c r="G33" s="4"/>
-      <x:c r="H33" s="4"/>
-      <x:c r="I33" s="4"/>
-      <x:c r="J33" s="4"/>
-      <x:c r="K33" s="4"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="4"/>
-      <x:c r="B34" s="4"/>
-      <x:c r="C34" s="4"/>
-      <x:c r="D34" s="4"/>
-      <x:c r="E34" s="4"/>
-      <x:c r="F34" s="4"/>
-      <x:c r="G34" s="4"/>
-      <x:c r="H34" s="4"/>
-      <x:c r="I34" s="4"/>
-      <x:c r="J34" s="4"/>
-      <x:c r="K34" s="4"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="4"/>
-      <x:c r="B35" s="4"/>
-      <x:c r="C35" s="4"/>
-      <x:c r="D35" s="4"/>
-      <x:c r="E35" s="4"/>
-      <x:c r="F35" s="4"/>
-      <x:c r="G35" s="4"/>
-      <x:c r="H35" s="4"/>
-      <x:c r="I35" s="4"/>
-      <x:c r="J35" s="4"/>
-      <x:c r="K35" s="4"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="4"/>
-      <x:c r="B36" s="4"/>
-      <x:c r="C36" s="4"/>
-      <x:c r="D36" s="4"/>
-      <x:c r="E36" s="4"/>
-      <x:c r="F36" s="4"/>
-      <x:c r="G36" s="4"/>
-      <x:c r="H36" s="4"/>
-      <x:c r="I36" s="4"/>
-      <x:c r="J36" s="4"/>
-      <x:c r="K36" s="4"/>
-    </x:row>
     <x:row r="37">
       <x:c r="A37" s="4"/>
       <x:c r="B37" s="4"/>
@@ -2002,2114 +6593,46 @@
     <x:mergeCell ref="A1:K1"/>
     <x:mergeCell ref="A2:K2"/>
   </x:mergeCells>
+  <x:conditionalFormatting sqref="F6:F25">
+    <x:cfRule type="dataBar" priority="1">
+      <x:dataBar>
+        <x:cfvo type="min"/>
+        <x:cfvo type="max"/>
+        <x:color rgb="FFF59E0B"/>
+      </x:dataBar>
+      <x:extLst>
+        <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{1CE81B44-A755-1404-1E86-F5FEF8F09A36}</x14:id>
+        </x:ext>
+      </x:extLst>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="G6:G25">
+      <x:formula1>"Ready,Invite sent,Active,Won,Review"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R74f79b65ee424cb4"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R30cf9e835fca4341"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb2242bcc715144c1"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R73ae64a30b6440ae"/>
   </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="9" t="str">
-        <x:v>MATCH PLANNER</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="4"/>
-      <x:c r="K1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="17" t="str">
-        <x:v>One-row-per-match buyer workspace. No imported schedule dependency; all rows are editable.</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
-      <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
-      <x:c r="H2" s="4"/>
-      <x:c r="I2" s="4"/>
-      <x:c r="J2" s="4"/>
-      <x:c r="K2" s="4"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="4"/>
-      <x:c r="B3" s="4"/>
-      <x:c r="C3" s="4"/>
-      <x:c r="D3" s="4"/>
-      <x:c r="E3" s="4"/>
-      <x:c r="F3" s="4"/>
-      <x:c r="G3" s="4"/>
-      <x:c r="H3" s="4"/>
-      <x:c r="I3" s="4"/>
-      <x:c r="J3" s="4"/>
-      <x:c r="K3" s="4"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="4"/>
-      <x:c r="B4" s="4"/>
-      <x:c r="C4" s="4"/>
-      <x:c r="D4" s="4"/>
-      <x:c r="E4" s="4"/>
-      <x:c r="F4" s="4"/>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
-      <x:c r="K4" s="4"/>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="26" t="str">
-        <x:v>Match ID</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
-        <x:v>Phase</x:v>
-      </x:c>
-      <x:c r="C5" s="26" t="str">
-        <x:v>Side A</x:v>
-      </x:c>
-      <x:c r="D5" s="26" t="str">
-        <x:v>Side B</x:v>
-      </x:c>
-      <x:c r="E5" s="26" t="str">
-        <x:v>Prediction</x:v>
-      </x:c>
-      <x:c r="F5" s="26" t="str">
-        <x:v>Signal</x:v>
-      </x:c>
-      <x:c r="G5" s="26" t="str">
-        <x:v>Confidence</x:v>
-      </x:c>
-      <x:c r="H5" s="26" t="str">
-        <x:v>Priority</x:v>
-      </x:c>
-      <x:c r="I5" s="26" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>M001</x:v>
-      </x:c>
-      <x:c r="B6" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D6" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E6" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F6" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G6" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H6" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I6" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J6" s="4"/>
-      <x:c r="K6" s="4"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>M002</x:v>
-      </x:c>
-      <x:c r="B7" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D7" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E7" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F7" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G7" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H7" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I7" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J7" s="4"/>
-      <x:c r="K7" s="4"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>M003</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H8" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I8" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>M004</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H9" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I9" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J9" s="4"/>
-      <x:c r="K9" s="4"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>M005</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H10" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I10" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J10" s="4"/>
-      <x:c r="K10" s="4"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>M006</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F11" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H11" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I11" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>M007</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H12" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I12" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>M008</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F13" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H13" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I13" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="33" t="str">
-        <x:v>M009</x:v>
-      </x:c>
-      <x:c r="B14" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D14" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E14" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F14" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G14" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H14" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I14" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="33" t="str">
-        <x:v>M010</x:v>
-      </x:c>
-      <x:c r="B15" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D15" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E15" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F15" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G15" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H15" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I15" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="33" t="str">
-        <x:v>M011</x:v>
-      </x:c>
-      <x:c r="B16" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D16" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E16" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F16" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G16" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H16" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I16" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="33" t="str">
-        <x:v>M012</x:v>
-      </x:c>
-      <x:c r="B17" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D17" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E17" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F17" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G17" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H17" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I17" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="A18" s="33" t="str">
-        <x:v>M013</x:v>
-      </x:c>
-      <x:c r="B18" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D18" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E18" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F18" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G18" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H18" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I18" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>M014</x:v>
-      </x:c>
-      <x:c r="B19" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D19" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E19" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F19" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G19" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H19" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I19" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J19" s="4"/>
-      <x:c r="K19" s="4"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="33" t="str">
-        <x:v>M015</x:v>
-      </x:c>
-      <x:c r="B20" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D20" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E20" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F20" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G20" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H20" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I20" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J20" s="4"/>
-      <x:c r="K20" s="4"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="33" t="str">
-        <x:v>M016</x:v>
-      </x:c>
-      <x:c r="B21" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D21" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E21" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F21" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G21" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H21" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I21" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J21" s="4"/>
-      <x:c r="K21" s="4"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="33" t="str">
-        <x:v>M017</x:v>
-      </x:c>
-      <x:c r="B22" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D22" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E22" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F22" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G22" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H22" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I22" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="33" t="str">
-        <x:v>M018</x:v>
-      </x:c>
-      <x:c r="B23" s="33" t="str">
-        <x:v>Group Stage</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D23" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E23" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F23" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G23" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H23" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I23" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J23" s="4"/>
-      <x:c r="K23" s="4"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="33" t="str">
-        <x:v>M019</x:v>
-      </x:c>
-      <x:c r="B24" s="33" t="str">
-        <x:v>Knockout</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D24" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E24" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F24" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G24" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H24" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I24" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="33" t="str">
-        <x:v>M020</x:v>
-      </x:c>
-      <x:c r="B25" s="33" t="str">
-        <x:v>Knockout</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D25" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E25" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F25" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G25" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H25" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I25" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="33" t="str">
-        <x:v>M021</x:v>
-      </x:c>
-      <x:c r="B26" s="33" t="str">
-        <x:v>Knockout</x:v>
-      </x:c>
-      <x:c r="C26" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D26" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E26" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F26" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G26" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H26" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I26" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="33" t="str">
-        <x:v>M022</x:v>
-      </x:c>
-      <x:c r="B27" s="33" t="str">
-        <x:v>Knockout</x:v>
-      </x:c>
-      <x:c r="C27" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D27" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E27" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F27" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G27" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H27" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I27" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J27" s="4"/>
-      <x:c r="K27" s="4"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="33" t="str">
-        <x:v>M023</x:v>
-      </x:c>
-      <x:c r="B28" s="33" t="str">
-        <x:v>Knockout</x:v>
-      </x:c>
-      <x:c r="C28" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D28" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E28" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F28" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G28" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H28" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I28" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J28" s="4"/>
-      <x:c r="K28" s="4"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="33" t="str">
-        <x:v>M024</x:v>
-      </x:c>
-      <x:c r="B29" s="33" t="str">
-        <x:v>Knockout</x:v>
-      </x:c>
-      <x:c r="C29" s="33" t="str">
-        <x:v>Team A</x:v>
-      </x:c>
-      <x:c r="D29" s="33" t="str">
-        <x:v>Team B</x:v>
-      </x:c>
-      <x:c r="E29" s="33" t="str">
-        <x:v>My Score</x:v>
-      </x:c>
-      <x:c r="F29" s="33" t="str">
-        <x:v>AI Signal</x:v>
-      </x:c>
-      <x:c r="G29" s="33" t="str">
-        <x:v>Confidence %</x:v>
-      </x:c>
-      <x:c r="H29" s="33" t="str">
-        <x:v>Watch Priority</x:v>
-      </x:c>
-      <x:c r="I29" s="33" t="str">
-        <x:v>Notes</x:v>
-      </x:c>
-      <x:c r="J29" s="4"/>
-      <x:c r="K29" s="4"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="4"/>
-      <x:c r="B30" s="4"/>
-      <x:c r="C30" s="4"/>
-      <x:c r="D30" s="4"/>
-      <x:c r="E30" s="4"/>
-      <x:c r="F30" s="4"/>
-      <x:c r="G30" s="4"/>
-      <x:c r="H30" s="4"/>
-      <x:c r="I30" s="4"/>
-      <x:c r="J30" s="4"/>
-      <x:c r="K30" s="4"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="4"/>
-      <x:c r="B31" s="4"/>
-      <x:c r="C31" s="4"/>
-      <x:c r="D31" s="4"/>
-      <x:c r="E31" s="4"/>
-      <x:c r="F31" s="4"/>
-      <x:c r="G31" s="4"/>
-      <x:c r="H31" s="4"/>
-      <x:c r="I31" s="4"/>
-      <x:c r="J31" s="4"/>
-      <x:c r="K31" s="4"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="4"/>
-      <x:c r="B32" s="4"/>
-      <x:c r="C32" s="4"/>
-      <x:c r="D32" s="4"/>
-      <x:c r="E32" s="4"/>
-      <x:c r="F32" s="4"/>
-      <x:c r="G32" s="4"/>
-      <x:c r="H32" s="4"/>
-      <x:c r="I32" s="4"/>
-      <x:c r="J32" s="4"/>
-      <x:c r="K32" s="4"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="4"/>
-      <x:c r="B33" s="4"/>
-      <x:c r="C33" s="4"/>
-      <x:c r="D33" s="4"/>
-      <x:c r="E33" s="4"/>
-      <x:c r="F33" s="4"/>
-      <x:c r="G33" s="4"/>
-      <x:c r="H33" s="4"/>
-      <x:c r="I33" s="4"/>
-      <x:c r="J33" s="4"/>
-      <x:c r="K33" s="4"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="4"/>
-      <x:c r="B34" s="4"/>
-      <x:c r="C34" s="4"/>
-      <x:c r="D34" s="4"/>
-      <x:c r="E34" s="4"/>
-      <x:c r="F34" s="4"/>
-      <x:c r="G34" s="4"/>
-      <x:c r="H34" s="4"/>
-      <x:c r="I34" s="4"/>
-      <x:c r="J34" s="4"/>
-      <x:c r="K34" s="4"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="4"/>
-      <x:c r="B35" s="4"/>
-      <x:c r="C35" s="4"/>
-      <x:c r="D35" s="4"/>
-      <x:c r="E35" s="4"/>
-      <x:c r="F35" s="4"/>
-      <x:c r="G35" s="4"/>
-      <x:c r="H35" s="4"/>
-      <x:c r="I35" s="4"/>
-      <x:c r="J35" s="4"/>
-      <x:c r="K35" s="4"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="4"/>
-      <x:c r="B36" s="4"/>
-      <x:c r="C36" s="4"/>
-      <x:c r="D36" s="4"/>
-      <x:c r="E36" s="4"/>
-      <x:c r="F36" s="4"/>
-      <x:c r="G36" s="4"/>
-      <x:c r="H36" s="4"/>
-      <x:c r="I36" s="4"/>
-      <x:c r="J36" s="4"/>
-      <x:c r="K36" s="4"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="4"/>
-      <x:c r="B37" s="4"/>
-      <x:c r="C37" s="4"/>
-      <x:c r="D37" s="4"/>
-      <x:c r="E37" s="4"/>
-      <x:c r="F37" s="4"/>
-      <x:c r="G37" s="4"/>
-      <x:c r="H37" s="4"/>
-      <x:c r="I37" s="4"/>
-      <x:c r="J37" s="4"/>
-      <x:c r="K37" s="4"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="4"/>
-      <x:c r="B38" s="4"/>
-      <x:c r="C38" s="4"/>
-      <x:c r="D38" s="4"/>
-      <x:c r="E38" s="4"/>
-      <x:c r="F38" s="4"/>
-      <x:c r="G38" s="4"/>
-      <x:c r="H38" s="4"/>
-      <x:c r="I38" s="4"/>
-      <x:c r="J38" s="4"/>
-      <x:c r="K38" s="4"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="4"/>
-      <x:c r="B39" s="4"/>
-      <x:c r="C39" s="4"/>
-      <x:c r="D39" s="4"/>
-      <x:c r="E39" s="4"/>
-      <x:c r="F39" s="4"/>
-      <x:c r="G39" s="4"/>
-      <x:c r="H39" s="4"/>
-      <x:c r="I39" s="4"/>
-      <x:c r="J39" s="4"/>
-      <x:c r="K39" s="4"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="4"/>
-      <x:c r="B40" s="4"/>
-      <x:c r="C40" s="4"/>
-      <x:c r="D40" s="4"/>
-      <x:c r="E40" s="4"/>
-      <x:c r="F40" s="4"/>
-      <x:c r="G40" s="4"/>
-      <x:c r="H40" s="4"/>
-      <x:c r="I40" s="4"/>
-      <x:c r="J40" s="4"/>
-      <x:c r="K40" s="4"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="4"/>
-      <x:c r="B41" s="4"/>
-      <x:c r="C41" s="4"/>
-      <x:c r="D41" s="4"/>
-      <x:c r="E41" s="4"/>
-      <x:c r="F41" s="4"/>
-      <x:c r="G41" s="4"/>
-      <x:c r="H41" s="4"/>
-      <x:c r="I41" s="4"/>
-      <x:c r="J41" s="4"/>
-      <x:c r="K41" s="4"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="4"/>
-      <x:c r="B42" s="4"/>
-      <x:c r="C42" s="4"/>
-      <x:c r="D42" s="4"/>
-      <x:c r="E42" s="4"/>
-      <x:c r="F42" s="4"/>
-      <x:c r="G42" s="4"/>
-      <x:c r="H42" s="4"/>
-      <x:c r="I42" s="4"/>
-      <x:c r="J42" s="4"/>
-      <x:c r="K42" s="4"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="4"/>
-      <x:c r="B43" s="4"/>
-      <x:c r="C43" s="4"/>
-      <x:c r="D43" s="4"/>
-      <x:c r="E43" s="4"/>
-      <x:c r="F43" s="4"/>
-      <x:c r="G43" s="4"/>
-      <x:c r="H43" s="4"/>
-      <x:c r="I43" s="4"/>
-      <x:c r="J43" s="4"/>
-      <x:c r="K43" s="4"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="4"/>
-      <x:c r="B44" s="4"/>
-      <x:c r="C44" s="4"/>
-      <x:c r="D44" s="4"/>
-      <x:c r="E44" s="4"/>
-      <x:c r="F44" s="4"/>
-      <x:c r="G44" s="4"/>
-      <x:c r="H44" s="4"/>
-      <x:c r="I44" s="4"/>
-      <x:c r="J44" s="4"/>
-      <x:c r="K44" s="4"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="4"/>
-      <x:c r="B45" s="4"/>
-      <x:c r="C45" s="4"/>
-      <x:c r="D45" s="4"/>
-      <x:c r="E45" s="4"/>
-      <x:c r="F45" s="4"/>
-      <x:c r="G45" s="4"/>
-      <x:c r="H45" s="4"/>
-      <x:c r="I45" s="4"/>
-      <x:c r="J45" s="4"/>
-      <x:c r="K45" s="4"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="4"/>
-      <x:c r="B46" s="4"/>
-      <x:c r="C46" s="4"/>
-      <x:c r="D46" s="4"/>
-      <x:c r="E46" s="4"/>
-      <x:c r="F46" s="4"/>
-      <x:c r="G46" s="4"/>
-      <x:c r="H46" s="4"/>
-      <x:c r="I46" s="4"/>
-      <x:c r="J46" s="4"/>
-      <x:c r="K46" s="4"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="4"/>
-      <x:c r="B47" s="4"/>
-      <x:c r="C47" s="4"/>
-      <x:c r="D47" s="4"/>
-      <x:c r="E47" s="4"/>
-      <x:c r="F47" s="4"/>
-      <x:c r="G47" s="4"/>
-      <x:c r="H47" s="4"/>
-      <x:c r="I47" s="4"/>
-      <x:c r="J47" s="4"/>
-      <x:c r="K47" s="4"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="4"/>
-      <x:c r="B48" s="4"/>
-      <x:c r="C48" s="4"/>
-      <x:c r="D48" s="4"/>
-      <x:c r="E48" s="4"/>
-      <x:c r="F48" s="4"/>
-      <x:c r="G48" s="4"/>
-      <x:c r="H48" s="4"/>
-      <x:c r="I48" s="4"/>
-      <x:c r="J48" s="4"/>
-      <x:c r="K48" s="4"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="4"/>
-      <x:c r="B49" s="4"/>
-      <x:c r="C49" s="4"/>
-      <x:c r="D49" s="4"/>
-      <x:c r="E49" s="4"/>
-      <x:c r="F49" s="4"/>
-      <x:c r="G49" s="4"/>
-      <x:c r="H49" s="4"/>
-      <x:c r="I49" s="4"/>
-      <x:c r="J49" s="4"/>
-      <x:c r="K49" s="4"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="4"/>
-      <x:c r="B50" s="4"/>
-      <x:c r="C50" s="4"/>
-      <x:c r="D50" s="4"/>
-      <x:c r="E50" s="4"/>
-      <x:c r="F50" s="4"/>
-      <x:c r="G50" s="4"/>
-      <x:c r="H50" s="4"/>
-      <x:c r="I50" s="4"/>
-      <x:c r="J50" s="4"/>
-      <x:c r="K50" s="4"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="A51" s="4"/>
-      <x:c r="B51" s="4"/>
-      <x:c r="C51" s="4"/>
-      <x:c r="D51" s="4"/>
-      <x:c r="E51" s="4"/>
-      <x:c r="F51" s="4"/>
-      <x:c r="G51" s="4"/>
-      <x:c r="H51" s="4"/>
-      <x:c r="I51" s="4"/>
-      <x:c r="J51" s="4"/>
-      <x:c r="K51" s="4"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="A52" s="4"/>
-      <x:c r="B52" s="4"/>
-      <x:c r="C52" s="4"/>
-      <x:c r="D52" s="4"/>
-      <x:c r="E52" s="4"/>
-      <x:c r="F52" s="4"/>
-      <x:c r="G52" s="4"/>
-      <x:c r="H52" s="4"/>
-      <x:c r="I52" s="4"/>
-      <x:c r="J52" s="4"/>
-      <x:c r="K52" s="4"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="A53" s="4"/>
-      <x:c r="B53" s="4"/>
-      <x:c r="C53" s="4"/>
-      <x:c r="D53" s="4"/>
-      <x:c r="E53" s="4"/>
-      <x:c r="F53" s="4"/>
-      <x:c r="G53" s="4"/>
-      <x:c r="H53" s="4"/>
-      <x:c r="I53" s="4"/>
-      <x:c r="J53" s="4"/>
-      <x:c r="K53" s="4"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="A54" s="4"/>
-      <x:c r="B54" s="4"/>
-      <x:c r="C54" s="4"/>
-      <x:c r="D54" s="4"/>
-      <x:c r="E54" s="4"/>
-      <x:c r="F54" s="4"/>
-      <x:c r="G54" s="4"/>
-      <x:c r="H54" s="4"/>
-      <x:c r="I54" s="4"/>
-      <x:c r="J54" s="4"/>
-      <x:c r="K54" s="4"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="A55" s="4"/>
-      <x:c r="B55" s="4"/>
-      <x:c r="C55" s="4"/>
-      <x:c r="D55" s="4"/>
-      <x:c r="E55" s="4"/>
-      <x:c r="F55" s="4"/>
-      <x:c r="G55" s="4"/>
-      <x:c r="H55" s="4"/>
-      <x:c r="I55" s="4"/>
-      <x:c r="J55" s="4"/>
-      <x:c r="K55" s="4"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="A56" s="4"/>
-      <x:c r="B56" s="4"/>
-      <x:c r="C56" s="4"/>
-      <x:c r="D56" s="4"/>
-      <x:c r="E56" s="4"/>
-      <x:c r="F56" s="4"/>
-      <x:c r="G56" s="4"/>
-      <x:c r="H56" s="4"/>
-      <x:c r="I56" s="4"/>
-      <x:c r="J56" s="4"/>
-      <x:c r="K56" s="4"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="A57" s="4"/>
-      <x:c r="B57" s="4"/>
-      <x:c r="C57" s="4"/>
-      <x:c r="D57" s="4"/>
-      <x:c r="E57" s="4"/>
-      <x:c r="F57" s="4"/>
-      <x:c r="G57" s="4"/>
-      <x:c r="H57" s="4"/>
-      <x:c r="I57" s="4"/>
-      <x:c r="J57" s="4"/>
-      <x:c r="K57" s="4"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="A58" s="4"/>
-      <x:c r="B58" s="4"/>
-      <x:c r="C58" s="4"/>
-      <x:c r="D58" s="4"/>
-      <x:c r="E58" s="4"/>
-      <x:c r="F58" s="4"/>
-      <x:c r="G58" s="4"/>
-      <x:c r="H58" s="4"/>
-      <x:c r="I58" s="4"/>
-      <x:c r="J58" s="4"/>
-      <x:c r="K58" s="4"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="A59" s="4"/>
-      <x:c r="B59" s="4"/>
-      <x:c r="C59" s="4"/>
-      <x:c r="D59" s="4"/>
-      <x:c r="E59" s="4"/>
-      <x:c r="F59" s="4"/>
-      <x:c r="G59" s="4"/>
-      <x:c r="H59" s="4"/>
-      <x:c r="I59" s="4"/>
-      <x:c r="J59" s="4"/>
-      <x:c r="K59" s="4"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="A60" s="4"/>
-      <x:c r="B60" s="4"/>
-      <x:c r="C60" s="4"/>
-      <x:c r="D60" s="4"/>
-      <x:c r="E60" s="4"/>
-      <x:c r="F60" s="4"/>
-      <x:c r="G60" s="4"/>
-      <x:c r="H60" s="4"/>
-      <x:c r="I60" s="4"/>
-      <x:c r="J60" s="4"/>
-      <x:c r="K60" s="4"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:K1"/>
-    <x:mergeCell ref="A2:K2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra2a0069e057148e7"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="34" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="9" t="str">
-        <x:v>FRIENDS LEAGUE</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
-      <x:c r="E1" s="4"/>
-      <x:c r="F1" s="4"/>
-      <x:c r="G1" s="4"/>
-      <x:c r="H1" s="4"/>
-      <x:c r="I1" s="4"/>
-      <x:c r="J1" s="4"/>
-      <x:c r="K1" s="4"/>
-    </x:row>
-    <x:row r="2" ht="22" customHeight="1">
-      <x:c r="A2" s="17" t="str">
-        <x:v>Private league board for AI vs Me / friends challenge. Static, editable, printable.</x:v>
-      </x:c>
-      <x:c r="B2" s="4"/>
-      <x:c r="C2" s="4"/>
-      <x:c r="D2" s="4"/>
-      <x:c r="E2" s="4"/>
-      <x:c r="F2" s="4"/>
-      <x:c r="G2" s="4"/>
-      <x:c r="H2" s="4"/>
-      <x:c r="I2" s="4"/>
-      <x:c r="J2" s="4"/>
-      <x:c r="K2" s="4"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="4"/>
-      <x:c r="B3" s="4"/>
-      <x:c r="C3" s="4"/>
-      <x:c r="D3" s="4"/>
-      <x:c r="E3" s="4"/>
-      <x:c r="F3" s="4"/>
-      <x:c r="G3" s="4"/>
-      <x:c r="H3" s="4"/>
-      <x:c r="I3" s="4"/>
-      <x:c r="J3" s="4"/>
-      <x:c r="K3" s="4"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="4"/>
-      <x:c r="B4" s="4"/>
-      <x:c r="C4" s="4"/>
-      <x:c r="D4" s="4"/>
-      <x:c r="E4" s="4"/>
-      <x:c r="F4" s="4"/>
-      <x:c r="G4" s="4"/>
-      <x:c r="H4" s="4"/>
-      <x:c r="I4" s="4"/>
-      <x:c r="J4" s="4"/>
-      <x:c r="K4" s="4"/>
-    </x:row>
-    <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="26" t="str">
-        <x:v>Player</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
-        <x:v>Role</x:v>
-      </x:c>
-      <x:c r="C5" s="26" t="str">
-        <x:v>Correct Scores</x:v>
-      </x:c>
-      <x:c r="D5" s="26" t="str">
-        <x:v>Correct Winners</x:v>
-      </x:c>
-      <x:c r="E5" s="26" t="str">
-        <x:v>Upsets Hit</x:v>
-      </x:c>
-      <x:c r="F5" s="26" t="str">
-        <x:v>Total Points</x:v>
-      </x:c>
-      <x:c r="G5" s="26" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="H5" s="4"/>
-      <x:c r="I5" s="4"/>
-      <x:c r="J5" s="4"/>
-      <x:c r="K5" s="4"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>Me</x:v>
-      </x:c>
-      <x:c r="B6" s="33" t="str">
-        <x:v>Owner</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D6" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E6" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F6" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="33" t="str">
-        <x:v>Ready</x:v>
-      </x:c>
-      <x:c r="H6" s="4"/>
-      <x:c r="I6" s="4"/>
-      <x:c r="J6" s="4"/>
-      <x:c r="K6" s="4"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="33" t="str">
-        <x:v>AI Scout</x:v>
-      </x:c>
-      <x:c r="B7" s="33" t="str">
-        <x:v>Benchmark</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D7" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E7" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F7" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="33" t="str">
-        <x:v>Ready</x:v>
-      </x:c>
-      <x:c r="H7" s="4"/>
-      <x:c r="I7" s="4"/>
-      <x:c r="J7" s="4"/>
-      <x:c r="K7" s="4"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>Friend 01</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>Player</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D8" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E8" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F8" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="33" t="str">
-        <x:v>Invite sent</x:v>
-      </x:c>
-      <x:c r="H8" s="4"/>
-      <x:c r="I8" s="4"/>
-      <x:c r="J8" s="4"/>
-      <x:c r="K8" s="4"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>Friend 02</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>Player</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D9" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E9" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F9" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="33" t="str">
-        <x:v>Invite sent</x:v>
-      </x:c>
-      <x:c r="H9" s="4"/>
-      <x:c r="I9" s="4"/>
-      <x:c r="J9" s="4"/>
-      <x:c r="K9" s="4"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>Friend 03</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>Player</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D10" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E10" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F10" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="33" t="str">
-        <x:v>Invite sent</x:v>
-      </x:c>
-      <x:c r="H10" s="4"/>
-      <x:c r="I10" s="4"/>
-      <x:c r="J10" s="4"/>
-      <x:c r="K10" s="4"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>Friend 04</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>Player</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D11" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E11" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F11" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="33" t="str">
-        <x:v>Invite sent</x:v>
-      </x:c>
-      <x:c r="H11" s="4"/>
-      <x:c r="I11" s="4"/>
-      <x:c r="J11" s="4"/>
-      <x:c r="K11" s="4"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>Friend 05</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>Player</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D12" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E12" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F12" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="33" t="str">
-        <x:v>Invite sent</x:v>
-      </x:c>
-      <x:c r="H12" s="4"/>
-      <x:c r="I12" s="4"/>
-      <x:c r="J12" s="4"/>
-      <x:c r="K12" s="4"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>Friend 06</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>Player</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D13" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E13" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F13" s="33" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="33" t="str">
-        <x:v>Invite sent</x:v>
-      </x:c>
-      <x:c r="H13" s="4"/>
-      <x:c r="I13" s="4"/>
-      <x:c r="J13" s="4"/>
-      <x:c r="K13" s="4"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-      <x:c r="F14" s="4"/>
-      <x:c r="G14" s="4"/>
-      <x:c r="H14" s="4"/>
-      <x:c r="I14" s="4"/>
-      <x:c r="J14" s="4"/>
-      <x:c r="K14" s="4"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="4"/>
-      <x:c r="B15" s="4"/>
-      <x:c r="C15" s="4"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-      <x:c r="F15" s="4"/>
-      <x:c r="G15" s="4"/>
-      <x:c r="H15" s="4"/>
-      <x:c r="I15" s="4"/>
-      <x:c r="J15" s="4"/>
-      <x:c r="K15" s="4"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
-      <x:c r="E16" s="4"/>
-      <x:c r="F16" s="4"/>
-      <x:c r="G16" s="4"/>
-      <x:c r="H16" s="4"/>
-      <x:c r="I16" s="4"/>
-      <x:c r="J16" s="4"/>
-      <x:c r="K16" s="4"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
-      <x:c r="E17" s="4"/>
-      <x:c r="F17" s="4"/>
-      <x:c r="G17" s="4"/>
-      <x:c r="H17" s="4"/>
-      <x:c r="I17" s="4"/>
-      <x:c r="J17" s="4"/>
-      <x:c r="K17" s="4"/>
-    </x:row>
-    <x:row r="18" ht="22" customHeight="1">
-      <x:c r="A18" s="50" t="str">
-        <x:v>Rule</x:v>
-      </x:c>
-      <x:c r="B18" s="50" t="str">
-        <x:v>Points</x:v>
-      </x:c>
-      <x:c r="C18" s="50" t="str">
-        <x:v>Definition</x:v>
-      </x:c>
-      <x:c r="D18" s="4"/>
-      <x:c r="E18" s="4"/>
-      <x:c r="F18" s="4"/>
-      <x:c r="G18" s="4"/>
-      <x:c r="H18" s="4"/>
-      <x:c r="I18" s="4"/>
-      <x:c r="J18" s="4"/>
-      <x:c r="K18" s="4"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="A19" s="33" t="str">
-        <x:v>Correct score</x:v>
-      </x:c>
-      <x:c r="B19" s="33" t="str">
-        <x:v>3 pts</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="str">
-        <x:v>Exact result prediction</x:v>
-      </x:c>
-      <x:c r="D19" s="4"/>
-      <x:c r="E19" s="4"/>
-      <x:c r="F19" s="4"/>
-      <x:c r="G19" s="4"/>
-      <x:c r="H19" s="4"/>
-      <x:c r="I19" s="4"/>
-      <x:c r="J19" s="4"/>
-      <x:c r="K19" s="4"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="A20" s="33" t="str">
-        <x:v>Correct winner</x:v>
-      </x:c>
-      <x:c r="B20" s="33" t="str">
-        <x:v>1 pt</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="str">
-        <x:v>Winner/draw direction correct</x:v>
-      </x:c>
-      <x:c r="D20" s="4"/>
-      <x:c r="E20" s="4"/>
-      <x:c r="F20" s="4"/>
-      <x:c r="G20" s="4"/>
-      <x:c r="H20" s="4"/>
-      <x:c r="I20" s="4"/>
-      <x:c r="J20" s="4"/>
-      <x:c r="K20" s="4"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="A21" s="33" t="str">
-        <x:v>Upset bonus</x:v>
-      </x:c>
-      <x:c r="B21" s="33" t="str">
-        <x:v>2 pts</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="str">
-        <x:v>Underdog marker lands</x:v>
-      </x:c>
-      <x:c r="D21" s="4"/>
-      <x:c r="E21" s="4"/>
-      <x:c r="F21" s="4"/>
-      <x:c r="G21" s="4"/>
-      <x:c r="H21" s="4"/>
-      <x:c r="I21" s="4"/>
-      <x:c r="J21" s="4"/>
-      <x:c r="K21" s="4"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="A22" s="33" t="str">
-        <x:v>Final champion</x:v>
-      </x:c>
-      <x:c r="B22" s="33" t="str">
-        <x:v>5 pts</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="str">
-        <x:v>Champion lock correct</x:v>
-      </x:c>
-      <x:c r="D22" s="4"/>
-      <x:c r="E22" s="4"/>
-      <x:c r="F22" s="4"/>
-      <x:c r="G22" s="4"/>
-      <x:c r="H22" s="4"/>
-      <x:c r="I22" s="4"/>
-      <x:c r="J22" s="4"/>
-      <x:c r="K22" s="4"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="A23" s="4"/>
-      <x:c r="B23" s="4"/>
-      <x:c r="C23" s="4"/>
-      <x:c r="D23" s="4"/>
-      <x:c r="E23" s="4"/>
-      <x:c r="F23" s="4"/>
-      <x:c r="G23" s="4"/>
-      <x:c r="H23" s="4"/>
-      <x:c r="I23" s="4"/>
-      <x:c r="J23" s="4"/>
-      <x:c r="K23" s="4"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="A24" s="4"/>
-      <x:c r="B24" s="4"/>
-      <x:c r="C24" s="4"/>
-      <x:c r="D24" s="4"/>
-      <x:c r="E24" s="4"/>
-      <x:c r="F24" s="4"/>
-      <x:c r="G24" s="4"/>
-      <x:c r="H24" s="4"/>
-      <x:c r="I24" s="4"/>
-      <x:c r="J24" s="4"/>
-      <x:c r="K24" s="4"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="A25" s="4"/>
-      <x:c r="B25" s="4"/>
-      <x:c r="C25" s="4"/>
-      <x:c r="D25" s="4"/>
-      <x:c r="E25" s="4"/>
-      <x:c r="F25" s="4"/>
-      <x:c r="G25" s="4"/>
-      <x:c r="H25" s="4"/>
-      <x:c r="I25" s="4"/>
-      <x:c r="J25" s="4"/>
-      <x:c r="K25" s="4"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="A26" s="4"/>
-      <x:c r="B26" s="4"/>
-      <x:c r="C26" s="4"/>
-      <x:c r="D26" s="4"/>
-      <x:c r="E26" s="4"/>
-      <x:c r="F26" s="4"/>
-      <x:c r="G26" s="4"/>
-      <x:c r="H26" s="4"/>
-      <x:c r="I26" s="4"/>
-      <x:c r="J26" s="4"/>
-      <x:c r="K26" s="4"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" s="4"/>
-      <x:c r="B27" s="4"/>
-      <x:c r="C27" s="4"/>
-      <x:c r="D27" s="4"/>
-      <x:c r="E27" s="4"/>
-      <x:c r="F27" s="4"/>
-      <x:c r="G27" s="4"/>
-      <x:c r="H27" s="4"/>
-      <x:c r="I27" s="4"/>
-      <x:c r="J27" s="4"/>
-      <x:c r="K27" s="4"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="A28" s="4"/>
-      <x:c r="B28" s="4"/>
-      <x:c r="C28" s="4"/>
-      <x:c r="D28" s="4"/>
-      <x:c r="E28" s="4"/>
-      <x:c r="F28" s="4"/>
-      <x:c r="G28" s="4"/>
-      <x:c r="H28" s="4"/>
-      <x:c r="I28" s="4"/>
-      <x:c r="J28" s="4"/>
-      <x:c r="K28" s="4"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="A29" s="4"/>
-      <x:c r="B29" s="4"/>
-      <x:c r="C29" s="4"/>
-      <x:c r="D29" s="4"/>
-      <x:c r="E29" s="4"/>
-      <x:c r="F29" s="4"/>
-      <x:c r="G29" s="4"/>
-      <x:c r="H29" s="4"/>
-      <x:c r="I29" s="4"/>
-      <x:c r="J29" s="4"/>
-      <x:c r="K29" s="4"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="A30" s="4"/>
-      <x:c r="B30" s="4"/>
-      <x:c r="C30" s="4"/>
-      <x:c r="D30" s="4"/>
-      <x:c r="E30" s="4"/>
-      <x:c r="F30" s="4"/>
-      <x:c r="G30" s="4"/>
-      <x:c r="H30" s="4"/>
-      <x:c r="I30" s="4"/>
-      <x:c r="J30" s="4"/>
-      <x:c r="K30" s="4"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="A31" s="4"/>
-      <x:c r="B31" s="4"/>
-      <x:c r="C31" s="4"/>
-      <x:c r="D31" s="4"/>
-      <x:c r="E31" s="4"/>
-      <x:c r="F31" s="4"/>
-      <x:c r="G31" s="4"/>
-      <x:c r="H31" s="4"/>
-      <x:c r="I31" s="4"/>
-      <x:c r="J31" s="4"/>
-      <x:c r="K31" s="4"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="A32" s="4"/>
-      <x:c r="B32" s="4"/>
-      <x:c r="C32" s="4"/>
-      <x:c r="D32" s="4"/>
-      <x:c r="E32" s="4"/>
-      <x:c r="F32" s="4"/>
-      <x:c r="G32" s="4"/>
-      <x:c r="H32" s="4"/>
-      <x:c r="I32" s="4"/>
-      <x:c r="J32" s="4"/>
-      <x:c r="K32" s="4"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="A33" s="4"/>
-      <x:c r="B33" s="4"/>
-      <x:c r="C33" s="4"/>
-      <x:c r="D33" s="4"/>
-      <x:c r="E33" s="4"/>
-      <x:c r="F33" s="4"/>
-      <x:c r="G33" s="4"/>
-      <x:c r="H33" s="4"/>
-      <x:c r="I33" s="4"/>
-      <x:c r="J33" s="4"/>
-      <x:c r="K33" s="4"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="A34" s="4"/>
-      <x:c r="B34" s="4"/>
-      <x:c r="C34" s="4"/>
-      <x:c r="D34" s="4"/>
-      <x:c r="E34" s="4"/>
-      <x:c r="F34" s="4"/>
-      <x:c r="G34" s="4"/>
-      <x:c r="H34" s="4"/>
-      <x:c r="I34" s="4"/>
-      <x:c r="J34" s="4"/>
-      <x:c r="K34" s="4"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="A35" s="4"/>
-      <x:c r="B35" s="4"/>
-      <x:c r="C35" s="4"/>
-      <x:c r="D35" s="4"/>
-      <x:c r="E35" s="4"/>
-      <x:c r="F35" s="4"/>
-      <x:c r="G35" s="4"/>
-      <x:c r="H35" s="4"/>
-      <x:c r="I35" s="4"/>
-      <x:c r="J35" s="4"/>
-      <x:c r="K35" s="4"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="A36" s="4"/>
-      <x:c r="B36" s="4"/>
-      <x:c r="C36" s="4"/>
-      <x:c r="D36" s="4"/>
-      <x:c r="E36" s="4"/>
-      <x:c r="F36" s="4"/>
-      <x:c r="G36" s="4"/>
-      <x:c r="H36" s="4"/>
-      <x:c r="I36" s="4"/>
-      <x:c r="J36" s="4"/>
-      <x:c r="K36" s="4"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="A37" s="4"/>
-      <x:c r="B37" s="4"/>
-      <x:c r="C37" s="4"/>
-      <x:c r="D37" s="4"/>
-      <x:c r="E37" s="4"/>
-      <x:c r="F37" s="4"/>
-      <x:c r="G37" s="4"/>
-      <x:c r="H37" s="4"/>
-      <x:c r="I37" s="4"/>
-      <x:c r="J37" s="4"/>
-      <x:c r="K37" s="4"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="A38" s="4"/>
-      <x:c r="B38" s="4"/>
-      <x:c r="C38" s="4"/>
-      <x:c r="D38" s="4"/>
-      <x:c r="E38" s="4"/>
-      <x:c r="F38" s="4"/>
-      <x:c r="G38" s="4"/>
-      <x:c r="H38" s="4"/>
-      <x:c r="I38" s="4"/>
-      <x:c r="J38" s="4"/>
-      <x:c r="K38" s="4"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="A39" s="4"/>
-      <x:c r="B39" s="4"/>
-      <x:c r="C39" s="4"/>
-      <x:c r="D39" s="4"/>
-      <x:c r="E39" s="4"/>
-      <x:c r="F39" s="4"/>
-      <x:c r="G39" s="4"/>
-      <x:c r="H39" s="4"/>
-      <x:c r="I39" s="4"/>
-      <x:c r="J39" s="4"/>
-      <x:c r="K39" s="4"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="A40" s="4"/>
-      <x:c r="B40" s="4"/>
-      <x:c r="C40" s="4"/>
-      <x:c r="D40" s="4"/>
-      <x:c r="E40" s="4"/>
-      <x:c r="F40" s="4"/>
-      <x:c r="G40" s="4"/>
-      <x:c r="H40" s="4"/>
-      <x:c r="I40" s="4"/>
-      <x:c r="J40" s="4"/>
-      <x:c r="K40" s="4"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="A41" s="4"/>
-      <x:c r="B41" s="4"/>
-      <x:c r="C41" s="4"/>
-      <x:c r="D41" s="4"/>
-      <x:c r="E41" s="4"/>
-      <x:c r="F41" s="4"/>
-      <x:c r="G41" s="4"/>
-      <x:c r="H41" s="4"/>
-      <x:c r="I41" s="4"/>
-      <x:c r="J41" s="4"/>
-      <x:c r="K41" s="4"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="A42" s="4"/>
-      <x:c r="B42" s="4"/>
-      <x:c r="C42" s="4"/>
-      <x:c r="D42" s="4"/>
-      <x:c r="E42" s="4"/>
-      <x:c r="F42" s="4"/>
-      <x:c r="G42" s="4"/>
-      <x:c r="H42" s="4"/>
-      <x:c r="I42" s="4"/>
-      <x:c r="J42" s="4"/>
-      <x:c r="K42" s="4"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="A43" s="4"/>
-      <x:c r="B43" s="4"/>
-      <x:c r="C43" s="4"/>
-      <x:c r="D43" s="4"/>
-      <x:c r="E43" s="4"/>
-      <x:c r="F43" s="4"/>
-      <x:c r="G43" s="4"/>
-      <x:c r="H43" s="4"/>
-      <x:c r="I43" s="4"/>
-      <x:c r="J43" s="4"/>
-      <x:c r="K43" s="4"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="A44" s="4"/>
-      <x:c r="B44" s="4"/>
-      <x:c r="C44" s="4"/>
-      <x:c r="D44" s="4"/>
-      <x:c r="E44" s="4"/>
-      <x:c r="F44" s="4"/>
-      <x:c r="G44" s="4"/>
-      <x:c r="H44" s="4"/>
-      <x:c r="I44" s="4"/>
-      <x:c r="J44" s="4"/>
-      <x:c r="K44" s="4"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="A45" s="4"/>
-      <x:c r="B45" s="4"/>
-      <x:c r="C45" s="4"/>
-      <x:c r="D45" s="4"/>
-      <x:c r="E45" s="4"/>
-      <x:c r="F45" s="4"/>
-      <x:c r="G45" s="4"/>
-      <x:c r="H45" s="4"/>
-      <x:c r="I45" s="4"/>
-      <x:c r="J45" s="4"/>
-      <x:c r="K45" s="4"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="A46" s="4"/>
-      <x:c r="B46" s="4"/>
-      <x:c r="C46" s="4"/>
-      <x:c r="D46" s="4"/>
-      <x:c r="E46" s="4"/>
-      <x:c r="F46" s="4"/>
-      <x:c r="G46" s="4"/>
-      <x:c r="H46" s="4"/>
-      <x:c r="I46" s="4"/>
-      <x:c r="J46" s="4"/>
-      <x:c r="K46" s="4"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="A47" s="4"/>
-      <x:c r="B47" s="4"/>
-      <x:c r="C47" s="4"/>
-      <x:c r="D47" s="4"/>
-      <x:c r="E47" s="4"/>
-      <x:c r="F47" s="4"/>
-      <x:c r="G47" s="4"/>
-      <x:c r="H47" s="4"/>
-      <x:c r="I47" s="4"/>
-      <x:c r="J47" s="4"/>
-      <x:c r="K47" s="4"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="A48" s="4"/>
-      <x:c r="B48" s="4"/>
-      <x:c r="C48" s="4"/>
-      <x:c r="D48" s="4"/>
-      <x:c r="E48" s="4"/>
-      <x:c r="F48" s="4"/>
-      <x:c r="G48" s="4"/>
-      <x:c r="H48" s="4"/>
-      <x:c r="I48" s="4"/>
-      <x:c r="J48" s="4"/>
-      <x:c r="K48" s="4"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="A49" s="4"/>
-      <x:c r="B49" s="4"/>
-      <x:c r="C49" s="4"/>
-      <x:c r="D49" s="4"/>
-      <x:c r="E49" s="4"/>
-      <x:c r="F49" s="4"/>
-      <x:c r="G49" s="4"/>
-      <x:c r="H49" s="4"/>
-      <x:c r="I49" s="4"/>
-      <x:c r="J49" s="4"/>
-      <x:c r="K49" s="4"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="A50" s="4"/>
-      <x:c r="B50" s="4"/>
-      <x:c r="C50" s="4"/>
-      <x:c r="D50" s="4"/>
-      <x:c r="E50" s="4"/>
-      <x:c r="F50" s="4"/>
-      <x:c r="G50" s="4"/>
-      <x:c r="H50" s="4"/>
-      <x:c r="I50" s="4"/>
-      <x:c r="J50" s="4"/>
-      <x:c r="K50" s="4"/>
-    </x:row>
-  </x:sheetData>
-  <x:mergeCells>
-    <x:mergeCell ref="A1:K1"/>
-    <x:mergeCell ref="A2:K2"/>
-  </x:mergeCells>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="2">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbddf99f03514b2c"/>
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2857ba95023d41db"/>
-  </x:tableParts>
+  <x:extLst>
+    <x:ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting>
+          <x14:cfRule type="dataBar" priority="1" id="{1CE81B44-A755-1404-1E86-F5FEF8F09A36}">
+            <x14:dataBar gradient="1">
+              <x14:cfvo type="min"/>
+              <x14:cfvo type="max"/>
+              <x14:fillColor rgb="FFF59E0B"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F6:F25</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </x:ext>
+  </x:extLst>
 </x:worksheet>
 </file>
 
@@ -4117,12 +6640,12 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="20" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="44" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
     <x:col min="8" max="8" width="15" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
@@ -4143,6 +6666,15 @@
       <x:c r="H1" s="66" t="str"/>
       <x:c r="I1" s="66" t="str"/>
       <x:c r="J1" s="66" t="str"/>
+      <x:c r="K1" s="105" t="str">
+        <x:v>Navigation</x:v>
+      </x:c>
+      <x:c r="L1" s="105" t="e">
+        <x:f>HYPERLINK("#'START_HERE'!A1","Back to START")</x:f>
+      </x:c>
+      <x:c r="M1" s="105" t="e">
+        <x:f>HYPERLINK("#'MATCH_PLANNER'!A1","104 Matches")</x:f>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="4"/>
@@ -4157,34 +6689,34 @@
       <x:c r="J2" s="4"/>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
-      <x:c r="A3" s="26" t="str">
+      <x:c r="A3" s="79" t="str">
         <x:v>annex_id</x:v>
       </x:c>
-      <x:c r="B3" s="26" t="str">
+      <x:c r="B3" s="79" t="str">
         <x:v>module</x:v>
       </x:c>
-      <x:c r="C3" s="26" t="str">
+      <x:c r="C3" s="79" t="str">
         <x:v>record_type</x:v>
       </x:c>
-      <x:c r="D3" s="26" t="str">
+      <x:c r="D3" s="79" t="str">
         <x:v>code</x:v>
       </x:c>
-      <x:c r="E3" s="26" t="str">
+      <x:c r="E3" s="79" t="str">
         <x:v>label</x:v>
       </x:c>
-      <x:c r="F3" s="26" t="str">
+      <x:c r="F3" s="79" t="str">
         <x:v>buyer_copy</x:v>
       </x:c>
-      <x:c r="G3" s="26" t="str">
+      <x:c r="G3" s="79" t="str">
         <x:v>usage_context</x:v>
       </x:c>
-      <x:c r="H3" s="26" t="str">
+      <x:c r="H3" s="79" t="str">
         <x:v>status</x:v>
       </x:c>
-      <x:c r="I3" s="26" t="str">
+      <x:c r="I3" s="79" t="str">
         <x:v>source_mode</x:v>
       </x:c>
-      <x:c r="J3" s="26" t="str">
+      <x:c r="J3" s="79" t="str">
         <x:v>ip_safety_note</x:v>
       </x:c>
     </x:row>
@@ -20067,7 +22599,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfd64b6ef0f6c4371"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R499ff9b205404e31"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20076,10 +22608,10 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="18" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="20" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="14" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="76" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="38" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="28" hidden="0" customWidth="1"/>
@@ -20089,18 +22621,18 @@
     <x:col min="11" max="11" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" ht="34" customHeight="1">
-      <x:c r="A1" s="9" t="str">
-        <x:v>FIX6C STATIC ANNEXC QA</x:v>
-      </x:c>
-      <x:c r="B1" s="4"/>
-      <x:c r="C1" s="4"/>
-      <x:c r="D1" s="4"/>
+    <x:row r="1" ht="28" customHeight="1">
+      <x:c r="A1" s="71" t="str">
+        <x:v>HACKATHON SPREADSHEET QA — STATIC ENGINE</x:v>
+      </x:c>
+      <x:c r="B1" s="74"/>
+      <x:c r="C1" s="74"/>
+      <x:c r="D1" s="74"/>
       <x:c r="E1" s="4"/>
     </x:row>
     <x:row r="2" ht="22" customHeight="1">
       <x:c r="A2" s="17" t="str">
-        <x:v>Automated static dependency check.</x:v>
+        <x:v>Automated static dependency and demo-readiness check.</x:v>
       </x:c>
       <x:c r="B2" s="4"/>
       <x:c r="C2" s="4"/>
@@ -20114,156 +22646,206 @@
       <x:c r="D3" s="4"/>
       <x:c r="E3" s="4"/>
     </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="4"/>
-      <x:c r="B4" s="4"/>
-      <x:c r="C4" s="4"/>
-      <x:c r="D4" s="4"/>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="79" t="str">
+        <x:v>Check</x:v>
+      </x:c>
+      <x:c r="B4" s="79" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="C4" s="79" t="str">
+        <x:v>Result</x:v>
+      </x:c>
+      <x:c r="D4" s="79" t="str">
+        <x:v>Notes</x:v>
+      </x:c>
       <x:c r="E4" s="4"/>
     </x:row>
     <x:row r="5" ht="22" customHeight="1">
-      <x:c r="A5" s="26" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-      <x:c r="B5" s="26" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="C5" s="26" t="str">
-        <x:v>Result</x:v>
-      </x:c>
-      <x:c r="D5" s="4"/>
+      <x:c r="A5" s="89" t="str">
+        <x:v>Generated file</x:v>
+      </x:c>
+      <x:c r="B5" s="89" t="str">
+        <x:v>FIX6C_STATIC_ANNEXC_HACKATHON_READY.xlsx</x:v>
+      </x:c>
+      <x:c r="C5" s="89" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D5" s="90" t="str">
+        <x:v>Exported from patched XLSX source.</x:v>
+      </x:c>
       <x:c r="E5" s="4"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="33" t="str">
-        <x:v>Generated file</x:v>
-      </x:c>
-      <x:c r="B6" s="33" t="str">
-        <x:v>FIX6C_STATIC_ANNEXC.xlsx</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="str">
+      <x:c r="A6" s="84" t="str">
+        <x:v>Sheet count</x:v>
+      </x:c>
+      <x:c r="B6" s="84" t="n">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C6" s="84" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="D6" s="4"/>
+      <x:c r="D6" s="90" t="str">
+        <x:v>START_HERE, BRACKET_WAR_ROOM, MATCH_PLANNER, FRIENDS_LEAGUE, AnnexC_495_STATIC, QA_STATIC_CHECK</x:v>
+      </x:c>
       <x:c r="E6" s="4"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="33" t="str">
+      <x:c r="A7" s="84" t="str">
+        <x:v>MATCH_PLANNER coverage</x:v>
+      </x:c>
+      <x:c r="B7" s="84" t="str">
+        <x:v>M001–M104</x:v>
+      </x:c>
+      <x:c r="C7" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D7" s="90" t="str">
+        <x:v>104 visible match rows.</x:v>
+      </x:c>
+      <x:c r="E7" s="4"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="84" t="str">
+        <x:v>MATCH_PLANNER formula</x:v>
+      </x:c>
+      <x:c r="B8" s="84" t="str">
+        <x:v>K6:K109</x:v>
+      </x:c>
+      <x:c r="C8" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D8" s="90" t="str">
+        <x:v>Points formula = IF Result blank then blank; exact Prediction/Result match gives 3.</x:v>
+      </x:c>
+      <x:c r="E8" s="4"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="84" t="str">
+        <x:v>FRIENDS_LEAGUE formula</x:v>
+      </x:c>
+      <x:c r="B9" s="84" t="str">
+        <x:v>F6:F25</x:v>
+      </x:c>
+      <x:c r="C9" s="84" t="str">
+        <x:v>PASS</x:v>
+      </x:c>
+      <x:c r="D9" s="90" t="str">
+        <x:v>Total Points = Correct Scores*3 + Correct Winners*1 + Upsets Hit*2.</x:v>
+      </x:c>
+      <x:c r="E9" s="4"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="84" t="str">
         <x:v>AnnexC row count</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
+      <x:c r="B10" s="84" t="n">
         <x:v>495</x:v>
       </x:c>
-      <x:c r="C7" s="33" t="str">
+      <x:c r="C10" s="84" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="D7" s="4"/>
-      <x:c r="E7" s="4"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="33" t="str">
-        <x:v>AnnexC source mode</x:v>
-      </x:c>
-      <x:c r="B8" s="33" t="str">
-        <x:v>embedded ordinary cell values</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="str">
+      <x:c r="D10" s="90" t="str">
+        <x:v>Embedded ordinary cell values.</x:v>
+      </x:c>
+      <x:c r="E10" s="4"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="84" t="str">
+        <x:v>Web functions</x:v>
+      </x:c>
+      <x:c r="B11" s="84" t="str">
+        <x:v>IMPORTHTML / IMPORTXML / IMPORTDATA / IMPORTRANGE absent</x:v>
+      </x:c>
+      <x:c r="C11" s="84" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="D8" s="4"/>
-      <x:c r="E8" s="4"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="33" t="str">
-        <x:v>Web functions</x:v>
-      </x:c>
-      <x:c r="B9" s="33" t="str">
-        <x:v>IMPORTHTML / IMPORTXML / IMPORTDATA / IMPORTRANGE absent</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="str">
+      <x:c r="D11" s="90" t="str">
+        <x:v>No live web dependency.</x:v>
+      </x:c>
+      <x:c r="E11" s="4"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="84" t="str">
+        <x:v>Array spill functions</x:v>
+      </x:c>
+      <x:c r="B12" s="84" t="str">
+        <x:v>ARRAYFORMULA / FILTER / QUERY / SORT / UNIQUE / TRANSPOSE absent</x:v>
+      </x:c>
+      <x:c r="C12" s="84" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="D9" s="4"/>
-      <x:c r="E9" s="4"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="33" t="str">
-        <x:v>Array spill functions</x:v>
-      </x:c>
-      <x:c r="B10" s="33" t="str">
-        <x:v>ARRAYFORMULA / FILTER / QUERY / SORT / UNIQUE / TRANSPOSE absent</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="str">
+      <x:c r="D12" s="90" t="str">
+        <x:v>No spill dependency.</x:v>
+      </x:c>
+      <x:c r="E12" s="4"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="84" t="str">
+        <x:v>Internal navigation</x:v>
+      </x:c>
+      <x:c r="B13" s="84" t="str">
+        <x:v>HYPERLINK formulas</x:v>
+      </x:c>
+      <x:c r="C13" s="84" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="D10" s="4"/>
-      <x:c r="E10" s="4"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="33" t="str">
-        <x:v>Known formula error tokens</x:v>
-      </x:c>
-      <x:c r="B11" s="33" t="str">
-        <x:v>#NAME? / #REF! / #DIV/0! / #VALUE! / #N/A absent</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="str">
+      <x:c r="D13" s="90" t="str">
+        <x:v>START_HERE, BRACKET_WAR_ROOM, MATCH_PLANNER, FRIENDS_LEAGUE navigation cells added.</x:v>
+      </x:c>
+      <x:c r="E13" s="4"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="90" t="str">
+        <x:v>Visible data-layer sheet</x:v>
+      </x:c>
+      <x:c r="B14" s="90" t="str">
+        <x:v>AnnexC_495_STATIC</x:v>
+      </x:c>
+      <x:c r="C14" s="90" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="33" t="str">
-        <x:v>Buyer visible tabs</x:v>
-      </x:c>
-      <x:c r="B12" s="33" t="str">
-        <x:v>START_HERE, BRACKET_WAR_ROOM, MATCH_PLANNER, FRIENDS_LEAGUE</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="str">
+      <x:c r="D14" s="90" t="str">
+        <x:v>Kept visible for hackathon proof-of-data-layer.</x:v>
+      </x:c>
+      <x:c r="E14" s="4"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="90" t="str">
+        <x:v>Internal QA sheet</x:v>
+      </x:c>
+      <x:c r="B15" s="90" t="str">
+        <x:v>QA_STATIC_CHECK</x:v>
+      </x:c>
+      <x:c r="C15" s="90" t="str">
+        <x:v>MANUAL</x:v>
+      </x:c>
+      <x:c r="D15" s="90" t="str">
+        <x:v>Hide in Google Sheets UI if desired after upload; artifact_tool export leaves sheet visible.</x:v>
+      </x:c>
+      <x:c r="E15" s="4"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="90" t="str">
+        <x:v>Claim boundary</x:v>
+      </x:c>
+      <x:c r="B16" s="90" t="str">
+        <x:v>static spreadsheet engine</x:v>
+      </x:c>
+      <x:c r="C16" s="90" t="str">
         <x:v>PASS</x:v>
       </x:c>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="33" t="str">
-        <x:v>Internal sheets</x:v>
-      </x:c>
-      <x:c r="B13" s="33" t="str">
-        <x:v>AnnexC_495_STATIC, QA_STATIC_CHECK</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="str">
-        <x:v>veryHidden after export</x:v>
-      </x:c>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="4"/>
-      <x:c r="B14" s="4"/>
-      <x:c r="C14" s="4"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="4"/>
-      <x:c r="B15" s="4"/>
-      <x:c r="C15" s="4"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="4"/>
-      <x:c r="B16" s="4"/>
-      <x:c r="C16" s="4"/>
-      <x:c r="D16" s="4"/>
+      <x:c r="D16" s="90" t="str">
+        <x:v>Do not claim live Google Sheets automation.</x:v>
+      </x:c>
       <x:c r="E16" s="4"/>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="4"/>
-      <x:c r="B17" s="4"/>
-      <x:c r="C17" s="4"/>
-      <x:c r="D17" s="4"/>
+      <x:c r="A17" s="90"/>
+      <x:c r="B17" s="90"/>
+      <x:c r="C17" s="90"/>
+      <x:c r="D17" s="90"/>
       <x:c r="E17" s="4"/>
     </x:row>
     <x:row r="18">
@@ -20294,7 +22876,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc307e9b1b94d42bd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8f8059e6bc1d4cd5"/>
   </x:tableParts>
 </x:worksheet>
 </file>